--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +923,6673 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128191292</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571980</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7144787</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128191284</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571958</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7145094</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128191236</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571866</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7144903</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128191235</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92047</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571958</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7144868</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På högre stubbe</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128191255</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571834</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7145195</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 st varnande</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128191261</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80168</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>572149</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7144695</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128191298</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>572163</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7144627</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i större område</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128191288</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571921</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7144953</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128191254</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>572189</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7144655</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128191269</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91346</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>571861</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7144892</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128191253</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>572126</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7144714</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på låga med bark</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128191273</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>571862</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7144828</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På nyligen fallen trädstam</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128191260</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>572163</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7144677</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128191286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>571922</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7144993</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128191246</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>571764</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7145073</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128191274</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>571787</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7145163</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på låga</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128191242</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>571758</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7145043</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128191258</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97351</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>571868</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7144822</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Stort område med många plantor</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128191266</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91346</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>572072</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7144777</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På högstubbe gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128191280</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>571879</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7144984</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128191297</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>572085</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7144743</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128191277</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>571951</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7144793</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128191282</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>571931</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7145109</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128191268</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91346</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>571872</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7144850</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128191257</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>571953</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7145103</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spår efter födosökande</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128191263</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>571949</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7144884</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128191248</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>571940</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7145031</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128191251</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>571965</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7144858</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128191271</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91346</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>572031</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7144801</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128191238</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>571774</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7145037</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128191243</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>571776</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7145163</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128191262</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>571946</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7144801</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>4 st födosökande</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128191270</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91346</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>571914</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7144954</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På stubbe och lågan</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128191299</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>571913</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7145011</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128191265</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>572072</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7144777</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128191272</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91346</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>572040</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7144775</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På högre stubbe och lågan</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128191259</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>572163</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7144677</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128191245</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>571798</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7145153</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128191275</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>571763</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7145074</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På högstubbe och lågan</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128191250</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>571954</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7145092</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128191256</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98489</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>572118</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7144737</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128191290</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>571947</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7144803</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128191293</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>572031</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7144794</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128191279</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>571825</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7145166</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128191285</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>571944</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7145060</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128191276</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>572105</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7144753</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128191252</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>571967</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7144855</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128191296</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>572052</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7144778</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128191295</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>572056</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7144776</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128191278</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>571873</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7144925</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128191264</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91346</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>571949</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7144884</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128191289</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>571956</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7144840</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128191281</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>571939</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7145031</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128191249</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>571989</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7145125</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128191241</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>571773</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7145038</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128191247</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>571767</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7145079</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128191267</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91346</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Norrån, Fjälltuna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>572045</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7144778</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191292</v>
+        <v>128191255</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,34 +936,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571980</v>
+        <v>571834</v>
       </c>
       <c r="R4" t="n">
-        <v>7144787</v>
+        <v>7145195</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,35 +1049,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191284</v>
+        <v>128191235</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>92047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
@@ -1070,7 +1090,7 @@
         <v>571958</v>
       </c>
       <c r="R5" t="n">
-        <v>7145094</v>
+        <v>7144868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1132,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,8 +1146,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1139,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191236</v>
+        <v>128191292</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,39 +1191,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571866</v>
+        <v>571980</v>
       </c>
       <c r="R6" t="n">
-        <v>7144903</v>
+        <v>7144787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,12 +1260,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,38 +1287,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191235</v>
+        <v>128191284</v>
       </c>
       <c r="B7" t="n">
-        <v>92047</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
@@ -1297,7 +1325,7 @@
         <v>571958</v>
       </c>
       <c r="R7" t="n">
-        <v>7144868</v>
+        <v>7145094</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,12 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På högre stubbe</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,24 +1376,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1387,46 +1394,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191255</v>
+        <v>128191261</v>
       </c>
       <c r="B8" t="n">
-        <v>57832</v>
+        <v>80168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1434,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571834</v>
+        <v>572149</v>
       </c>
       <c r="R8" t="n">
-        <v>7145195</v>
+        <v>7144695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,12 +1477,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 st varnande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,8 +1491,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1511,48 +1525,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191261</v>
+        <v>128191236</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572149</v>
+        <v>571866</v>
       </c>
       <c r="R9" t="n">
-        <v>7144695</v>
+        <v>7144903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,24 +1624,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128191246</v>
+        <v>128191274</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,39 +2603,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571764</v>
+        <v>571787</v>
       </c>
       <c r="R18" t="n">
-        <v>7145073</v>
+        <v>7145163</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2667,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2677,12 +2672,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla fruktkroppar på låga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2693,6 +2688,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2709,10 +2719,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128191274</v>
+        <v>128191246</v>
       </c>
       <c r="B19" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,34 +2730,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571787</v>
+        <v>571764</v>
       </c>
       <c r="R19" t="n">
-        <v>7145163</v>
+        <v>7145073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2794,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2804,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på låga</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,21 +2820,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2953,32 +2953,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128191258</v>
+        <v>128191266</v>
       </c>
       <c r="B21" t="n">
-        <v>97351</v>
+        <v>91346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571868</v>
+        <v>572072</v>
       </c>
       <c r="R21" t="n">
-        <v>7144822</v>
+        <v>7144777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Stort område med många plantor</t>
+          <t>På högstubbe gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3047,9 +3047,23 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3066,32 +3080,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128191266</v>
+        <v>128191258</v>
       </c>
       <c r="B22" t="n">
-        <v>91346</v>
+        <v>97351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3101,10 +3115,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572072</v>
+        <v>571868</v>
       </c>
       <c r="R22" t="n">
-        <v>7144777</v>
+        <v>7144822</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3136,7 +3150,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3146,12 +3160,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På högstubbe gran</t>
+          <t>Stort område med många plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3160,23 +3174,9 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191280</v>
+        <v>128191268</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>91346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571879</v>
+        <v>571872</v>
       </c>
       <c r="R23" t="n">
-        <v>7144984</v>
+        <v>7144850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,7 +3273,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,6 +3289,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3300,7 +3320,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191297</v>
+        <v>128191280</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -3335,10 +3355,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572085</v>
+        <v>571879</v>
       </c>
       <c r="R24" t="n">
-        <v>7144743</v>
+        <v>7144984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,7 +3390,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3380,7 +3400,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,7 +3427,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191277</v>
+        <v>128191297</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3442,10 +3462,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571951</v>
+        <v>572085</v>
       </c>
       <c r="R25" t="n">
-        <v>7144793</v>
+        <v>7144743</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,7 +3497,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,7 +3507,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,7 +3534,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191282</v>
+        <v>128191277</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3549,10 +3569,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571931</v>
+        <v>571951</v>
       </c>
       <c r="R26" t="n">
-        <v>7145109</v>
+        <v>7144793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3584,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3594,12 +3614,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3626,10 +3641,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128191268</v>
+        <v>128191282</v>
       </c>
       <c r="B27" t="n">
-        <v>91346</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3637,21 +3652,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3661,10 +3676,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571872</v>
+        <v>571931</v>
       </c>
       <c r="R27" t="n">
-        <v>7144850</v>
+        <v>7145109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3696,7 +3711,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3706,12 +3721,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På stubbe och låga</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3722,21 +3737,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191257</v>
+        <v>128191263</v>
       </c>
       <c r="B28" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,42 +3764,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571953</v>
+        <v>571949</v>
       </c>
       <c r="R28" t="n">
-        <v>7145103</v>
+        <v>7144884</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3831,7 +3823,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3841,12 +3833,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191263</v>
+        <v>128191248</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,34 +3871,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571949</v>
+        <v>571940</v>
       </c>
       <c r="R29" t="n">
-        <v>7144884</v>
+        <v>7145031</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3943,7 +3935,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3953,7 +3945,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,7 +3977,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191248</v>
+        <v>128191251</v>
       </c>
       <c r="B30" t="n">
         <v>57672</v>
@@ -4020,10 +4017,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571940</v>
+        <v>571965</v>
       </c>
       <c r="R30" t="n">
-        <v>7145031</v>
+        <v>7144858</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4055,7 +4052,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4065,12 +4062,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,10 +4094,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191251</v>
+        <v>128191257</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4108,16 +4105,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4126,21 +4123,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571965</v>
+        <v>571953</v>
       </c>
       <c r="R31" t="n">
-        <v>7144858</v>
+        <v>7145103</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,10 +4214,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191271</v>
+        <v>128191238</v>
       </c>
       <c r="B32" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,34 +4225,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572031</v>
+        <v>571774</v>
       </c>
       <c r="R32" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4284,7 +4289,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,12 +4299,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4310,21 +4315,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4341,7 +4331,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191238</v>
+        <v>128191243</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -4372,7 +4362,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4381,10 +4371,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571774</v>
+        <v>571776</v>
       </c>
       <c r="R33" t="n">
-        <v>7145037</v>
+        <v>7145163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4416,7 +4406,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4426,12 +4416,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4458,27 +4448,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191243</v>
+        <v>128191262</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>57776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4486,10 +4476,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4498,10 +4492,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571776</v>
+        <v>571946</v>
       </c>
       <c r="R34" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4533,7 +4527,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4543,12 +4537,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4575,51 +4569,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191262</v>
+        <v>128191271</v>
       </c>
       <c r="B35" t="n">
-        <v>57776</v>
+        <v>91346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571946</v>
+        <v>572031</v>
       </c>
       <c r="R35" t="n">
         <v>7144801</v>
@@ -4654,7 +4639,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,12 +4649,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,6 +4665,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4696,10 +4696,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128191270</v>
+        <v>128191299</v>
       </c>
       <c r="B36" t="n">
-        <v>91346</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571914</v>
+        <v>571913</v>
       </c>
       <c r="R36" t="n">
-        <v>7144954</v>
+        <v>7145011</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På stubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4792,21 +4792,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4823,10 +4808,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128191299</v>
+        <v>128191270</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>91346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4834,21 +4819,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4858,10 +4843,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>571913</v>
+        <v>571914</v>
       </c>
       <c r="R37" t="n">
-        <v>7145011</v>
+        <v>7144954</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4893,7 +4878,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4903,12 +4888,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe och lågan</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4919,6 +4904,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4935,10 +4935,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128191265</v>
+        <v>128191272</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>91346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4946,21 +4946,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572072</v>
+        <v>572040</v>
       </c>
       <c r="R38" t="n">
-        <v>7144777</v>
+        <v>7144775</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5015,7 +5015,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På högre stubbe och lågan</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5026,6 +5031,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5042,10 +5062,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128191272</v>
+        <v>128191265</v>
       </c>
       <c r="B39" t="n">
-        <v>91346</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5053,21 +5073,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5077,10 +5097,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572040</v>
+        <v>572072</v>
       </c>
       <c r="R39" t="n">
-        <v>7144775</v>
+        <v>7144777</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5112,7 +5132,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5122,12 +5142,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På högre stubbe och lågan</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5138,21 +5153,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5300,10 +5300,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191245</v>
+        <v>128191275</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5311,39 +5311,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571798</v>
+        <v>571763</v>
       </c>
       <c r="R41" t="n">
-        <v>7145153</v>
+        <v>7145074</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5375,7 +5370,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5385,12 +5380,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5401,6 +5396,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5417,10 +5427,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191275</v>
+        <v>128191290</v>
       </c>
       <c r="B42" t="n">
-        <v>91368</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5428,21 +5438,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5452,10 +5462,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571763</v>
+        <v>571947</v>
       </c>
       <c r="R42" t="n">
-        <v>7145074</v>
+        <v>7144803</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5487,7 +5497,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5497,12 +5507,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På högstubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5513,21 +5523,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5544,10 +5539,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191250</v>
+        <v>128191293</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,39 +5550,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571954</v>
+        <v>572031</v>
       </c>
       <c r="R43" t="n">
-        <v>7145092</v>
+        <v>7144794</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5619,7 +5609,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5629,12 +5619,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5661,61 +5646,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191256</v>
+        <v>128191245</v>
       </c>
       <c r="B44" t="n">
-        <v>98489</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572118</v>
+        <v>571798</v>
       </c>
       <c r="R44" t="n">
-        <v>7144737</v>
+        <v>7145153</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5747,7 +5721,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5757,7 +5731,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5766,7 +5745,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5785,10 +5763,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191290</v>
+        <v>128191250</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5796,34 +5774,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571947</v>
+        <v>571954</v>
       </c>
       <c r="R45" t="n">
-        <v>7144803</v>
+        <v>7145092</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5855,7 +5838,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5865,12 +5848,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5897,45 +5880,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191293</v>
+        <v>128191256</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>98489</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572031</v>
+        <v>572118</v>
       </c>
       <c r="R46" t="n">
-        <v>7144794</v>
+        <v>7144737</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5967,7 +5966,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5977,7 +5976,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5986,6 +5985,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128191279</v>
+        <v>128191276</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>571825</v>
+        <v>572105</v>
       </c>
       <c r="R47" t="n">
-        <v>7145166</v>
+        <v>7144753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6084,7 +6084,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6095,6 +6100,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6111,7 +6131,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191285</v>
+        <v>128191279</v>
       </c>
       <c r="B48" t="n">
         <v>79029</v>
@@ -6146,10 +6166,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571944</v>
+        <v>571825</v>
       </c>
       <c r="R48" t="n">
-        <v>7145060</v>
+        <v>7145166</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6181,7 +6201,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6191,7 +6211,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6218,10 +6238,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128191276</v>
+        <v>128191285</v>
       </c>
       <c r="B49" t="n">
-        <v>91368</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6229,21 +6249,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6253,10 +6273,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572105</v>
+        <v>571944</v>
       </c>
       <c r="R49" t="n">
-        <v>7144753</v>
+        <v>7145060</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6288,7 +6308,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6298,12 +6318,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På högstubbe</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6314,21 +6329,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6900,10 +6900,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128191289</v>
+        <v>128191267</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>91346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6911,21 +6911,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571956</v>
+        <v>572045</v>
       </c>
       <c r="R55" t="n">
-        <v>7144840</v>
+        <v>7144778</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6980,7 +6980,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6991,6 +6996,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7007,7 +7027,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128191281</v>
+        <v>128191289</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -7042,10 +7062,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571939</v>
+        <v>571956</v>
       </c>
       <c r="R56" t="n">
-        <v>7145031</v>
+        <v>7144840</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7077,7 +7097,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7087,7 +7107,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7114,10 +7134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128191249</v>
+        <v>128191281</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7125,39 +7145,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571989</v>
+        <v>571939</v>
       </c>
       <c r="R57" t="n">
-        <v>7145125</v>
+        <v>7145031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7189,7 +7204,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7199,12 +7214,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7231,7 +7241,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128191241</v>
+        <v>128191249</v>
       </c>
       <c r="B58" t="n">
         <v>57672</v>
@@ -7262,7 +7272,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7271,10 +7281,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571773</v>
+        <v>571989</v>
       </c>
       <c r="R58" t="n">
-        <v>7145038</v>
+        <v>7145125</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7306,7 +7316,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7316,12 +7326,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7348,7 +7358,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128191247</v>
+        <v>128191241</v>
       </c>
       <c r="B59" t="n">
         <v>57672</v>
@@ -7388,10 +7398,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571767</v>
+        <v>571773</v>
       </c>
       <c r="R59" t="n">
-        <v>7145079</v>
+        <v>7145038</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7423,7 +7433,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7433,12 +7443,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7465,10 +7475,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128191267</v>
+        <v>128191247</v>
       </c>
       <c r="B60" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7476,34 +7486,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572045</v>
+        <v>571767</v>
       </c>
       <c r="R60" t="n">
-        <v>7144778</v>
+        <v>7145079</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7535,7 +7550,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7545,12 +7560,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7561,21 +7576,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,46 +925,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191255</v>
+        <v>128191261</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>80168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571834</v>
+        <v>572149</v>
       </c>
       <c r="R4" t="n">
-        <v>7145195</v>
+        <v>7144695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1 st varnande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,8 +1022,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1049,48 +1056,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191235</v>
+        <v>128191292</v>
       </c>
       <c r="B5" t="n">
-        <v>92047</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571958</v>
+        <v>571980</v>
       </c>
       <c r="R5" t="n">
-        <v>7144868</v>
+        <v>7144787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,12 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På högre stubbe</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,24 +1145,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1180,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191292</v>
+        <v>128191284</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1215,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571980</v>
+        <v>571958</v>
       </c>
       <c r="R6" t="n">
-        <v>7144787</v>
+        <v>7145094</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191284</v>
+        <v>128191255</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,34 +1281,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571958</v>
+        <v>571834</v>
       </c>
       <c r="R7" t="n">
-        <v>7145094</v>
+        <v>7145195</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1362,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,48 +1394,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191261</v>
+        <v>128191236</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572149</v>
+        <v>571866</v>
       </c>
       <c r="R8" t="n">
-        <v>7144695</v>
+        <v>7144903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,12 +1479,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,24 +1493,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1525,50 +1511,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191236</v>
+        <v>128191235</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>92048</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571866</v>
+        <v>571958</v>
       </c>
       <c r="R9" t="n">
-        <v>7144903</v>
+        <v>7144868</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,8 +1608,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128191298</v>
+        <v>128191254</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,34 +1653,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572163</v>
+        <v>572189</v>
       </c>
       <c r="R10" t="n">
-        <v>7144627</v>
+        <v>7144655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1717,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,12 +1727,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig förekomst i större område</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1754,7 +1759,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128191288</v>
+        <v>128191298</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1789,10 +1794,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571921</v>
+        <v>572163</v>
       </c>
       <c r="R11" t="n">
-        <v>7144953</v>
+        <v>7144627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1829,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,12 +1839,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Riklig förekomst i större område</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128191254</v>
+        <v>128191288</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,39 +1882,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572189</v>
+        <v>571921</v>
       </c>
       <c r="R12" t="n">
-        <v>7144655</v>
+        <v>7144953</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,7 +1986,7 @@
         <v>128191269</v>
       </c>
       <c r="B13" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128191273</v>
       </c>
       <c r="B15" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128191274</v>
+        <v>128191246</v>
       </c>
       <c r="B18" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,34 +2603,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571787</v>
+        <v>571764</v>
       </c>
       <c r="R18" t="n">
-        <v>7145163</v>
+        <v>7145073</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2667,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,12 +2677,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på låga</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2688,21 +2693,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2719,10 +2709,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128191246</v>
+        <v>128191274</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,39 +2720,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571764</v>
+        <v>571787</v>
       </c>
       <c r="R19" t="n">
-        <v>7145073</v>
+        <v>7145163</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2794,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2804,12 +2789,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla fruktkroppar på låga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,6 +2805,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2956,7 +2956,7 @@
         <v>128191266</v>
       </c>
       <c r="B21" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>128191258</v>
       </c>
       <c r="B22" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191268</v>
+        <v>128191280</v>
       </c>
       <c r="B23" t="n">
-        <v>91346</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571872</v>
+        <v>571879</v>
       </c>
       <c r="R23" t="n">
-        <v>7144850</v>
+        <v>7144984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,12 +3273,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,21 +3284,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3320,7 +3300,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191280</v>
+        <v>128191297</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -3355,10 +3335,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571879</v>
+        <v>572085</v>
       </c>
       <c r="R24" t="n">
-        <v>7144984</v>
+        <v>7144743</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3390,7 +3370,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3400,7 +3380,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,7 +3407,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191297</v>
+        <v>128191277</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3462,10 +3442,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572085</v>
+        <v>571951</v>
       </c>
       <c r="R25" t="n">
-        <v>7144743</v>
+        <v>7144793</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3497,7 +3477,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3507,7 +3487,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,7 +3514,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191277</v>
+        <v>128191282</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3569,10 +3549,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571951</v>
+        <v>571931</v>
       </c>
       <c r="R26" t="n">
-        <v>7144793</v>
+        <v>7145109</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,7 +3584,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3614,7 +3594,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,10 +3626,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128191282</v>
+        <v>128191268</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>91347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3652,21 +3637,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3676,10 +3661,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571931</v>
+        <v>571872</v>
       </c>
       <c r="R27" t="n">
-        <v>7145109</v>
+        <v>7144850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3711,7 +3696,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,12 +3706,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3737,6 +3722,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191263</v>
+        <v>128191257</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,34 +3764,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571949</v>
+        <v>571953</v>
       </c>
       <c r="R28" t="n">
-        <v>7144884</v>
+        <v>7145103</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,7 +3831,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3841,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4094,10 +4107,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191257</v>
+        <v>128191263</v>
       </c>
       <c r="B31" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4105,42 +4118,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571953</v>
+        <v>571949</v>
       </c>
       <c r="R31" t="n">
-        <v>7145103</v>
+        <v>7144884</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4187,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,10 +4214,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191238</v>
+        <v>128191271</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>91347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,39 +4225,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571774</v>
+        <v>572031</v>
       </c>
       <c r="R32" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4289,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4299,12 +4294,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4315,6 +4310,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4331,27 +4341,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191243</v>
+        <v>128191262</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57776</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4359,10 +4369,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4371,10 +4385,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571776</v>
+        <v>571946</v>
       </c>
       <c r="R33" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,7 +4420,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4416,12 +4430,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4448,27 +4462,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191262</v>
+        <v>128191238</v>
       </c>
       <c r="B34" t="n">
-        <v>57776</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4476,14 +4490,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4492,10 +4502,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571946</v>
+        <v>571774</v>
       </c>
       <c r="R34" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4527,7 +4537,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4537,12 +4547,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4569,10 +4579,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191271</v>
+        <v>128191243</v>
       </c>
       <c r="B35" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4580,34 +4590,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572031</v>
+        <v>571776</v>
       </c>
       <c r="R35" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4639,7 +4654,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4649,12 +4664,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4665,21 +4680,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4696,10 +4696,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128191299</v>
+        <v>128191270</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>91347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571913</v>
+        <v>571914</v>
       </c>
       <c r="R36" t="n">
-        <v>7145011</v>
+        <v>7144954</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe och lågan</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4792,6 +4792,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4808,10 +4823,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128191270</v>
+        <v>128191299</v>
       </c>
       <c r="B37" t="n">
-        <v>91346</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4819,21 +4834,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4843,10 +4858,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>571914</v>
+        <v>571913</v>
       </c>
       <c r="R37" t="n">
-        <v>7144954</v>
+        <v>7145011</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4878,7 +4893,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4888,12 +4903,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På stubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4904,21 +4919,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4938,7 +4938,7 @@
         <v>128191272</v>
       </c>
       <c r="B38" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191275</v>
+        <v>128191245</v>
       </c>
       <c r="B41" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5311,34 +5311,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571763</v>
+        <v>571798</v>
       </c>
       <c r="R41" t="n">
-        <v>7145074</v>
+        <v>7145153</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5370,7 +5375,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5380,12 +5385,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På högstubbe och lågan</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5396,21 +5401,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5427,10 +5417,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191290</v>
+        <v>128191250</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5438,34 +5428,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571947</v>
+        <v>571954</v>
       </c>
       <c r="R42" t="n">
-        <v>7144803</v>
+        <v>7145092</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5497,7 +5492,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5507,12 +5502,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5539,7 +5534,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191293</v>
+        <v>128191290</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -5574,10 +5569,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572031</v>
+        <v>571947</v>
       </c>
       <c r="R43" t="n">
-        <v>7144794</v>
+        <v>7144803</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5609,7 +5604,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5619,7 +5614,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5646,10 +5646,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191245</v>
+        <v>128191275</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5657,39 +5657,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571798</v>
+        <v>571763</v>
       </c>
       <c r="R44" t="n">
-        <v>7145153</v>
+        <v>7145074</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5721,7 +5716,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5731,12 +5726,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5747,6 +5742,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5763,10 +5773,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191250</v>
+        <v>128191293</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5774,39 +5784,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571954</v>
+        <v>572031</v>
       </c>
       <c r="R45" t="n">
-        <v>7145092</v>
+        <v>7144794</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5838,7 +5843,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5848,12 +5853,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5883,7 +5883,7 @@
         <v>128191256</v>
       </c>
       <c r="B46" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128191276</v>
+        <v>128191252</v>
       </c>
       <c r="B47" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6015,34 +6015,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572105</v>
+        <v>571967</v>
       </c>
       <c r="R47" t="n">
-        <v>7144753</v>
+        <v>7144855</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6074,7 +6079,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6084,12 +6089,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6100,21 +6105,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6345,10 +6335,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128191252</v>
+        <v>128191276</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,39 +6346,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>571967</v>
+        <v>572105</v>
       </c>
       <c r="R50" t="n">
-        <v>7144855</v>
+        <v>7144753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6420,7 +6405,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6430,12 +6415,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6446,6 +6431,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6462,10 +6462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191296</v>
+        <v>128191264</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>91347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,21 +6473,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572052</v>
+        <v>571949</v>
       </c>
       <c r="R51" t="n">
-        <v>7144778</v>
+        <v>7144884</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,7 +6542,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6569,7 +6574,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128191295</v>
+        <v>128191278</v>
       </c>
       <c r="B52" t="n">
         <v>79029</v>
@@ -6604,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572056</v>
+        <v>571873</v>
       </c>
       <c r="R52" t="n">
-        <v>7144776</v>
+        <v>7144925</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6639,7 +6644,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6649,12 +6654,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6681,7 +6681,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128191278</v>
+        <v>128191296</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>571873</v>
+        <v>572052</v>
       </c>
       <c r="R53" t="n">
-        <v>7144925</v>
+        <v>7144778</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6788,10 +6788,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128191264</v>
+        <v>128191295</v>
       </c>
       <c r="B54" t="n">
-        <v>91346</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6799,21 +6799,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571949</v>
+        <v>572056</v>
       </c>
       <c r="R54" t="n">
-        <v>7144884</v>
+        <v>7144776</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6903,7 +6903,7 @@
         <v>128191267</v>
       </c>
       <c r="B55" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,48 +925,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191261</v>
+        <v>128191236</v>
       </c>
       <c r="B4" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572149</v>
+        <v>571866</v>
       </c>
       <c r="R4" t="n">
-        <v>7144695</v>
+        <v>7144903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,24 +1024,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,7 +1042,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191292</v>
+        <v>128191284</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1091,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571980</v>
+        <v>571958</v>
       </c>
       <c r="R5" t="n">
-        <v>7144787</v>
+        <v>7145094</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191284</v>
+        <v>128191292</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1198,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571958</v>
+        <v>571980</v>
       </c>
       <c r="R6" t="n">
-        <v>7145094</v>
+        <v>7144787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,46 +1256,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191255</v>
+        <v>128191235</v>
       </c>
       <c r="B7" t="n">
-        <v>57832</v>
+        <v>92049</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1317,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571834</v>
+        <v>571958</v>
       </c>
       <c r="R7" t="n">
-        <v>7145195</v>
+        <v>7144868</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,12 +1339,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 st varnande</t>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,8 +1353,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1394,50 +1387,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191236</v>
+        <v>128191261</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>80168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571866</v>
+        <v>572149</v>
       </c>
       <c r="R8" t="n">
-        <v>7144903</v>
+        <v>7144695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,8 +1484,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1511,37 +1518,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191235</v>
+        <v>128191255</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>57832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1549,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571958</v>
+        <v>571834</v>
       </c>
       <c r="R9" t="n">
-        <v>7144868</v>
+        <v>7145195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,24 +1624,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128191254</v>
+        <v>128191288</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,39 +1653,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572189</v>
+        <v>571921</v>
       </c>
       <c r="R10" t="n">
-        <v>7144655</v>
+        <v>7144953</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1717,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1727,12 +1722,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128191298</v>
+        <v>128191254</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,34 +1765,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572163</v>
+        <v>572189</v>
       </c>
       <c r="R11" t="n">
-        <v>7144627</v>
+        <v>7144655</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig förekomst i större område</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,7 +1871,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128191288</v>
+        <v>128191298</v>
       </c>
       <c r="B12" t="n">
         <v>79029</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571921</v>
+        <v>572163</v>
       </c>
       <c r="R12" t="n">
-        <v>7144953</v>
+        <v>7144627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Riklig förekomst i större område</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,7 +1986,7 @@
         <v>128191269</v>
       </c>
       <c r="B13" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128191273</v>
       </c>
       <c r="B15" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191260</v>
+        <v>128191286</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,37 +2365,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572163</v>
+        <v>571922</v>
       </c>
       <c r="R16" t="n">
-        <v>7144677</v>
+        <v>7144993</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,12 +2434,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal levande sälg</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,24 +2443,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2485,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128191286</v>
+        <v>128191260</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,34 +2472,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571922</v>
+        <v>572163</v>
       </c>
       <c r="R17" t="n">
-        <v>7144993</v>
+        <v>7144677</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2555,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2565,7 +2544,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,8 +2558,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128191246</v>
+        <v>128191274</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,39 +2603,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571764</v>
+        <v>571787</v>
       </c>
       <c r="R18" t="n">
-        <v>7145073</v>
+        <v>7145163</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2667,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2677,12 +2672,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla fruktkroppar på låga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2693,6 +2688,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2709,10 +2719,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128191274</v>
+        <v>128191246</v>
       </c>
       <c r="B19" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,34 +2730,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571787</v>
+        <v>571764</v>
       </c>
       <c r="R19" t="n">
-        <v>7145163</v>
+        <v>7145073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2794,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2804,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på låga</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,21 +2820,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128191242</v>
+        <v>128191266</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,39 +2847,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571758</v>
+        <v>572072</v>
       </c>
       <c r="R20" t="n">
-        <v>7145043</v>
+        <v>7144777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2911,7 +2906,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,12 +2916,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På högstubbe gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,6 +2932,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2953,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128191266</v>
+        <v>128191242</v>
       </c>
       <c r="B21" t="n">
-        <v>91347</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,34 +2974,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572072</v>
+        <v>571758</v>
       </c>
       <c r="R21" t="n">
-        <v>7144777</v>
+        <v>7145043</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3023,7 +3038,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3033,12 +3048,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På högstubbe gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3049,21 +3064,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3083,7 +3083,7 @@
         <v>128191258</v>
       </c>
       <c r="B22" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191297</v>
+        <v>128191277</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572085</v>
+        <v>571951</v>
       </c>
       <c r="R24" t="n">
-        <v>7144743</v>
+        <v>7144793</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,7 +3407,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191277</v>
+        <v>128191282</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571951</v>
+        <v>571931</v>
       </c>
       <c r="R25" t="n">
-        <v>7144793</v>
+        <v>7145109</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,7 +3487,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,7 +3519,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191282</v>
+        <v>128191297</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3549,10 +3554,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571931</v>
+        <v>572085</v>
       </c>
       <c r="R26" t="n">
-        <v>7145109</v>
+        <v>7144743</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3584,7 +3589,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3594,12 +3599,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3629,7 +3629,7 @@
         <v>128191268</v>
       </c>
       <c r="B27" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3873,10 +3873,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191248</v>
+        <v>128191263</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,39 +3884,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571940</v>
+        <v>571949</v>
       </c>
       <c r="R29" t="n">
-        <v>7145031</v>
+        <v>7144884</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3948,7 +3943,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3958,12 +3953,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3990,7 +3980,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191251</v>
+        <v>128191248</v>
       </c>
       <c r="B30" t="n">
         <v>57672</v>
@@ -4030,10 +4020,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571965</v>
+        <v>571940</v>
       </c>
       <c r="R30" t="n">
-        <v>7144858</v>
+        <v>7145031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,7 +4055,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4075,12 +4065,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4107,10 +4097,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191263</v>
+        <v>128191251</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,34 +4108,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571949</v>
+        <v>571965</v>
       </c>
       <c r="R31" t="n">
-        <v>7144884</v>
+        <v>7144858</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4177,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,7 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,10 +4214,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191271</v>
+        <v>128191238</v>
       </c>
       <c r="B32" t="n">
-        <v>91347</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,34 +4225,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572031</v>
+        <v>571774</v>
       </c>
       <c r="R32" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4284,7 +4289,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,12 +4299,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4310,21 +4315,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4341,27 +4331,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191262</v>
+        <v>128191243</v>
       </c>
       <c r="B33" t="n">
-        <v>57776</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4369,14 +4359,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4385,10 +4371,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571946</v>
+        <v>571776</v>
       </c>
       <c r="R33" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4420,7 +4406,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4430,12 +4416,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4462,27 +4448,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191238</v>
+        <v>128191262</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>57776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4490,10 +4476,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4502,10 +4492,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571774</v>
+        <v>571946</v>
       </c>
       <c r="R34" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4537,7 +4527,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4547,12 +4537,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4579,10 +4569,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191243</v>
+        <v>128191271</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4590,39 +4580,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571776</v>
+        <v>572031</v>
       </c>
       <c r="R35" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,7 +4639,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,12 +4649,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,6 +4665,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4696,10 +4696,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128191270</v>
+        <v>128191299</v>
       </c>
       <c r="B36" t="n">
-        <v>91347</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571914</v>
+        <v>571913</v>
       </c>
       <c r="R36" t="n">
-        <v>7144954</v>
+        <v>7145011</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På stubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4792,21 +4792,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4823,10 +4808,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128191299</v>
+        <v>128191270</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4834,21 +4819,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4858,10 +4843,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>571913</v>
+        <v>571914</v>
       </c>
       <c r="R37" t="n">
-        <v>7145011</v>
+        <v>7144954</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4893,7 +4878,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4903,12 +4888,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe och lågan</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4919,6 +4904,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4938,7 +4938,7 @@
         <v>128191272</v>
       </c>
       <c r="B38" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5534,45 +5534,61 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191290</v>
+        <v>128191256</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>98491</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571947</v>
+        <v>572118</v>
       </c>
       <c r="R43" t="n">
-        <v>7144803</v>
+        <v>7144737</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5604,7 +5620,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5614,12 +5630,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5628,6 +5639,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5649,7 +5661,7 @@
         <v>128191275</v>
       </c>
       <c r="B44" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5785,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191293</v>
+        <v>128191290</v>
       </c>
       <c r="B45" t="n">
         <v>79029</v>
@@ -5808,10 +5820,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572031</v>
+        <v>571947</v>
       </c>
       <c r="R45" t="n">
-        <v>7144794</v>
+        <v>7144803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5843,7 +5855,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5853,7 +5865,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5880,61 +5897,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191256</v>
+        <v>128191293</v>
       </c>
       <c r="B46" t="n">
-        <v>98490</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572118</v>
+        <v>572031</v>
       </c>
       <c r="R46" t="n">
-        <v>7144737</v>
+        <v>7144794</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5966,7 +5967,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5976,7 +5977,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5985,7 +5986,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128191252</v>
+        <v>128191276</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6015,39 +6015,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>571967</v>
+        <v>572105</v>
       </c>
       <c r="R47" t="n">
-        <v>7144855</v>
+        <v>7144753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6079,7 +6074,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6089,12 +6084,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6105,6 +6100,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6121,7 +6131,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191279</v>
+        <v>128191285</v>
       </c>
       <c r="B48" t="n">
         <v>79029</v>
@@ -6156,10 +6166,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571825</v>
+        <v>571944</v>
       </c>
       <c r="R48" t="n">
-        <v>7145166</v>
+        <v>7145060</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6191,7 +6201,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6201,7 +6211,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6228,7 +6238,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128191285</v>
+        <v>128191279</v>
       </c>
       <c r="B49" t="n">
         <v>79029</v>
@@ -6263,10 +6273,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571944</v>
+        <v>571825</v>
       </c>
       <c r="R49" t="n">
-        <v>7145060</v>
+        <v>7145166</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6298,7 +6308,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6308,7 +6318,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6335,10 +6345,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128191276</v>
+        <v>128191252</v>
       </c>
       <c r="B50" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6346,34 +6356,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572105</v>
+        <v>571967</v>
       </c>
       <c r="R50" t="n">
-        <v>7144753</v>
+        <v>7144855</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6405,7 +6420,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6415,12 +6430,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6431,21 +6446,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6462,10 +6462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191264</v>
+        <v>128191295</v>
       </c>
       <c r="B51" t="n">
-        <v>91347</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,21 +6473,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571949</v>
+        <v>572056</v>
       </c>
       <c r="R51" t="n">
-        <v>7144884</v>
+        <v>7144776</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6788,10 +6788,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128191295</v>
+        <v>128191264</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6799,21 +6799,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572056</v>
+        <v>571949</v>
       </c>
       <c r="R54" t="n">
-        <v>7144776</v>
+        <v>7144884</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6900,10 +6900,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128191267</v>
+        <v>128191281</v>
       </c>
       <c r="B55" t="n">
-        <v>91347</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6911,21 +6911,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572045</v>
+        <v>571939</v>
       </c>
       <c r="R55" t="n">
-        <v>7144778</v>
+        <v>7145031</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6980,12 +6980,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På högstubbe</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6996,21 +6991,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7134,10 +7114,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128191281</v>
+        <v>128191267</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7145,21 +7125,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7169,10 +7149,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571939</v>
+        <v>572045</v>
       </c>
       <c r="R57" t="n">
-        <v>7145031</v>
+        <v>7144778</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7204,7 +7184,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7214,7 +7194,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7225,6 +7210,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191236</v>
+        <v>128191284</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,39 +936,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571866</v>
+        <v>571958</v>
       </c>
       <c r="R4" t="n">
-        <v>7144903</v>
+        <v>7145094</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,12 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191284</v>
+        <v>128191292</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1077,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571958</v>
+        <v>571980</v>
       </c>
       <c r="R5" t="n">
-        <v>7145094</v>
+        <v>7144787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,45 +1139,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191292</v>
+        <v>128191235</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>92049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571980</v>
+        <v>571958</v>
       </c>
       <c r="R6" t="n">
-        <v>7144787</v>
+        <v>7144868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1222,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,8 +1236,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1256,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191235</v>
+        <v>128191261</v>
       </c>
       <c r="B7" t="n">
-        <v>92049</v>
+        <v>80168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571958</v>
+        <v>572149</v>
       </c>
       <c r="R7" t="n">
-        <v>7144868</v>
+        <v>7144695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,12 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,17 +1373,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1387,37 +1401,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191261</v>
+        <v>128191255</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>57832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1425,10 +1448,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572149</v>
+        <v>571834</v>
       </c>
       <c r="R8" t="n">
-        <v>7144695</v>
+        <v>7145195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1493,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,24 +1507,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1518,10 +1525,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191255</v>
+        <v>128191236</v>
       </c>
       <c r="B9" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,46 +1536,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571834</v>
+        <v>571866</v>
       </c>
       <c r="R9" t="n">
-        <v>7145195</v>
+        <v>7144903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 st varnande</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1754,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128191254</v>
+        <v>128191298</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,39 +1765,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572189</v>
+        <v>572163</v>
       </c>
       <c r="R11" t="n">
-        <v>7144655</v>
+        <v>7144627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,12 +1834,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst i större område</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128191298</v>
+        <v>128191254</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,34 +1877,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572163</v>
+        <v>572189</v>
       </c>
       <c r="R12" t="n">
-        <v>7144627</v>
+        <v>7144655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Riklig förekomst i större område</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191286</v>
+        <v>128191260</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,34 +2365,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571922</v>
+        <v>572163</v>
       </c>
       <c r="R16" t="n">
-        <v>7144993</v>
+        <v>7144677</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,7 +2437,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,8 +2451,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2461,10 +2485,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128191260</v>
+        <v>128191286</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,37 +2496,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572163</v>
+        <v>571922</v>
       </c>
       <c r="R17" t="n">
-        <v>7144677</v>
+        <v>7144993</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2555,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,12 +2565,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal levande sälg</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,24 +2574,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -3300,7 +3300,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191277</v>
+        <v>128191297</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571951</v>
+        <v>572085</v>
       </c>
       <c r="R24" t="n">
-        <v>7144793</v>
+        <v>7144743</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,7 +3407,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191282</v>
+        <v>128191277</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571931</v>
+        <v>571951</v>
       </c>
       <c r="R25" t="n">
-        <v>7145109</v>
+        <v>7144793</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,12 +3487,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3519,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191297</v>
+        <v>128191268</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,21 +3525,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3554,10 +3549,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572085</v>
+        <v>571872</v>
       </c>
       <c r="R26" t="n">
-        <v>7144743</v>
+        <v>7144850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3589,7 +3584,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3599,7 +3594,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3610,6 +3610,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3626,10 +3641,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128191268</v>
+        <v>128191282</v>
       </c>
       <c r="B27" t="n">
-        <v>91348</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3637,21 +3652,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3661,10 +3676,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571872</v>
+        <v>571931</v>
       </c>
       <c r="R27" t="n">
-        <v>7144850</v>
+        <v>7145109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3696,7 +3711,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3706,12 +3721,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På stubbe och låga</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3722,21 +3737,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191257</v>
+        <v>128191248</v>
       </c>
       <c r="B28" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,16 +3764,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3782,24 +3782,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571953</v>
+        <v>571940</v>
       </c>
       <c r="R28" t="n">
-        <v>7145103</v>
+        <v>7145031</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3831,7 +3828,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3841,12 +3838,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Spår efter födosökande</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,10 +3870,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191263</v>
+        <v>128191251</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,34 +3881,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571949</v>
+        <v>571965</v>
       </c>
       <c r="R29" t="n">
-        <v>7144884</v>
+        <v>7144858</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3943,7 +3945,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3953,7 +3955,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,10 +3987,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191248</v>
+        <v>128191263</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3991,39 +3998,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571940</v>
+        <v>571949</v>
       </c>
       <c r="R30" t="n">
-        <v>7145031</v>
+        <v>7144884</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4055,7 +4057,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4065,12 +4067,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,10 +4094,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191251</v>
+        <v>128191257</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4108,16 +4105,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4126,21 +4123,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571965</v>
+        <v>571953</v>
       </c>
       <c r="R31" t="n">
-        <v>7144858</v>
+        <v>7145103</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5300,50 +5300,61 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191245</v>
+        <v>128191256</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>98491</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571798</v>
+        <v>572118</v>
       </c>
       <c r="R41" t="n">
-        <v>7145153</v>
+        <v>7144737</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5375,7 +5386,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5385,12 +5396,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5399,6 +5405,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5417,10 +5424,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191250</v>
+        <v>128191275</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5428,39 +5435,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571954</v>
+        <v>571763</v>
       </c>
       <c r="R42" t="n">
-        <v>7145092</v>
+        <v>7145074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5492,7 +5494,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5502,12 +5504,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5518,6 +5520,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5534,61 +5551,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191256</v>
+        <v>128191293</v>
       </c>
       <c r="B43" t="n">
-        <v>98491</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572118</v>
+        <v>572031</v>
       </c>
       <c r="R43" t="n">
-        <v>7144737</v>
+        <v>7144794</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5620,7 +5621,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5630,7 +5631,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5639,7 +5640,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5658,10 +5658,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191275</v>
+        <v>128191290</v>
       </c>
       <c r="B44" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5669,21 +5669,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571763</v>
+        <v>571947</v>
       </c>
       <c r="R44" t="n">
-        <v>7145074</v>
+        <v>7144803</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På högstubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5754,21 +5754,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5785,10 +5770,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191290</v>
+        <v>128191245</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5796,34 +5781,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571947</v>
+        <v>571798</v>
       </c>
       <c r="R45" t="n">
-        <v>7144803</v>
+        <v>7145153</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5855,7 +5845,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5865,12 +5855,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5897,10 +5887,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191293</v>
+        <v>128191250</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5908,34 +5898,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572031</v>
+        <v>571954</v>
       </c>
       <c r="R46" t="n">
-        <v>7144794</v>
+        <v>7145092</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5967,7 +5962,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5977,7 +5972,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6462,10 +6462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191295</v>
+        <v>128191264</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,21 +6473,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572056</v>
+        <v>571949</v>
       </c>
       <c r="R51" t="n">
-        <v>7144776</v>
+        <v>7144884</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6574,7 +6574,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128191278</v>
+        <v>128191295</v>
       </c>
       <c r="B52" t="n">
         <v>79029</v>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571873</v>
+        <v>572056</v>
       </c>
       <c r="R52" t="n">
-        <v>7144925</v>
+        <v>7144776</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6654,7 +6654,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6788,10 +6793,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128191264</v>
+        <v>128191278</v>
       </c>
       <c r="B54" t="n">
-        <v>91348</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6799,21 +6804,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6823,10 +6828,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571949</v>
+        <v>571873</v>
       </c>
       <c r="R54" t="n">
-        <v>7144884</v>
+        <v>7144925</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6858,7 +6863,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6868,12 +6873,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På stubbe</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6900,10 +6900,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128191281</v>
+        <v>128191267</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6911,21 +6911,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571939</v>
+        <v>572045</v>
       </c>
       <c r="R55" t="n">
-        <v>7145031</v>
+        <v>7144778</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6980,7 +6980,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6991,6 +6996,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7114,10 +7134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128191267</v>
+        <v>128191281</v>
       </c>
       <c r="B57" t="n">
-        <v>91348</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7125,21 +7145,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7149,10 +7169,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572045</v>
+        <v>571939</v>
       </c>
       <c r="R57" t="n">
-        <v>7144778</v>
+        <v>7145031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7184,7 +7204,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7194,12 +7214,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På högstubbe</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7210,21 +7225,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191280</v>
+        <v>128191268</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571879</v>
+        <v>571872</v>
       </c>
       <c r="R23" t="n">
-        <v>7144984</v>
+        <v>7144850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,7 +3273,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,6 +3289,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3300,7 +3320,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191297</v>
+        <v>128191280</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -3335,10 +3355,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572085</v>
+        <v>571879</v>
       </c>
       <c r="R24" t="n">
-        <v>7144743</v>
+        <v>7144984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,7 +3390,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3380,7 +3400,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,7 +3427,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191277</v>
+        <v>128191297</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3442,10 +3462,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571951</v>
+        <v>572085</v>
       </c>
       <c r="R25" t="n">
-        <v>7144793</v>
+        <v>7144743</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,7 +3497,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,7 +3507,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191268</v>
+        <v>128191277</v>
       </c>
       <c r="B26" t="n">
-        <v>91348</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3525,21 +3545,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3549,10 +3569,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571872</v>
+        <v>571951</v>
       </c>
       <c r="R26" t="n">
-        <v>7144850</v>
+        <v>7144793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3584,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3594,12 +3614,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3610,21 +3625,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191248</v>
+        <v>128191257</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,16 +3764,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3782,21 +3782,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571940</v>
+        <v>571953</v>
       </c>
       <c r="R28" t="n">
-        <v>7145031</v>
+        <v>7145103</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3828,7 +3831,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3838,12 +3841,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,7 +3873,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191251</v>
+        <v>128191248</v>
       </c>
       <c r="B29" t="n">
         <v>57672</v>
@@ -3910,10 +3913,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571965</v>
+        <v>571940</v>
       </c>
       <c r="R29" t="n">
-        <v>7144858</v>
+        <v>7145031</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3945,7 +3948,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3955,12 +3958,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3987,10 +3990,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191263</v>
+        <v>128191251</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,34 +4001,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571949</v>
+        <v>571965</v>
       </c>
       <c r="R30" t="n">
-        <v>7144884</v>
+        <v>7144858</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4057,7 +4065,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4067,7 +4075,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,10 +4107,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191257</v>
+        <v>128191263</v>
       </c>
       <c r="B31" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4105,42 +4118,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571953</v>
+        <v>571949</v>
       </c>
       <c r="R31" t="n">
-        <v>7145103</v>
+        <v>7144884</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4187,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191268</v>
+        <v>128191280</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571872</v>
+        <v>571879</v>
       </c>
       <c r="R23" t="n">
-        <v>7144850</v>
+        <v>7144984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,12 +3273,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,21 +3284,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3320,7 +3300,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191280</v>
+        <v>128191297</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -3355,10 +3335,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571879</v>
+        <v>572085</v>
       </c>
       <c r="R24" t="n">
-        <v>7144984</v>
+        <v>7144743</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3390,7 +3370,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3400,7 +3380,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,7 +3407,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191297</v>
+        <v>128191277</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3462,10 +3442,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572085</v>
+        <v>571951</v>
       </c>
       <c r="R25" t="n">
-        <v>7144743</v>
+        <v>7144793</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3497,7 +3477,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3507,7 +3487,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191277</v>
+        <v>128191268</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3545,21 +3525,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3569,10 +3549,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571951</v>
+        <v>571872</v>
       </c>
       <c r="R26" t="n">
-        <v>7144793</v>
+        <v>7144850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,7 +3584,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3614,7 +3594,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3625,6 +3610,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -4214,27 +4214,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191238</v>
+        <v>128191262</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>57776</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4242,10 +4242,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4254,10 +4258,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571774</v>
+        <v>571946</v>
       </c>
       <c r="R32" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4289,7 +4293,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4299,12 +4303,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,7 +4335,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191243</v>
+        <v>128191238</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -4362,7 +4366,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4371,10 +4375,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571776</v>
+        <v>571774</v>
       </c>
       <c r="R33" t="n">
-        <v>7145163</v>
+        <v>7145037</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,7 +4410,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4416,12 +4420,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4448,27 +4452,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191262</v>
+        <v>128191243</v>
       </c>
       <c r="B34" t="n">
-        <v>57776</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4476,14 +4480,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571946</v>
+        <v>571776</v>
       </c>
       <c r="R34" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,35 +925,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191284</v>
+        <v>128191235</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>92049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
@@ -963,7 +966,7 @@
         <v>571958</v>
       </c>
       <c r="R4" t="n">
-        <v>7145094</v>
+        <v>7144868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,8 +1022,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1032,45 +1056,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191292</v>
+        <v>128191261</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571980</v>
+        <v>572149</v>
       </c>
       <c r="R5" t="n">
-        <v>7144787</v>
+        <v>7144695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1139,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,8 +1153,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1139,38 +1187,35 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191235</v>
+        <v>128191284</v>
       </c>
       <c r="B6" t="n">
-        <v>92049</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
@@ -1180,7 +1225,7 @@
         <v>571958</v>
       </c>
       <c r="R6" t="n">
-        <v>7144868</v>
+        <v>7145094</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1257,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,12 +1267,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På högre stubbe</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,24 +1276,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,48 +1294,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191261</v>
+        <v>128191236</v>
       </c>
       <c r="B7" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572149</v>
+        <v>571866</v>
       </c>
       <c r="R7" t="n">
-        <v>7144695</v>
+        <v>7144903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1379,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,24 +1393,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1525,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191236</v>
+        <v>128191292</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,39 +1546,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571866</v>
+        <v>571980</v>
       </c>
       <c r="R9" t="n">
-        <v>7144903</v>
+        <v>7144787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128191288</v>
+        <v>128191254</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,34 +1653,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571921</v>
+        <v>572189</v>
       </c>
       <c r="R10" t="n">
-        <v>7144953</v>
+        <v>7144655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1717,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,12 +1727,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1754,7 +1759,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128191298</v>
+        <v>128191288</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1789,10 +1794,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572163</v>
+        <v>571921</v>
       </c>
       <c r="R11" t="n">
-        <v>7144627</v>
+        <v>7144953</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1829,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,12 +1839,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig förekomst i större område</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128191254</v>
+        <v>128191298</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,39 +1882,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572189</v>
+        <v>572163</v>
       </c>
       <c r="R12" t="n">
-        <v>7144655</v>
+        <v>7144627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst i större område</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128191266</v>
+        <v>128191242</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,34 +2847,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572072</v>
+        <v>571758</v>
       </c>
       <c r="R20" t="n">
-        <v>7144777</v>
+        <v>7145043</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2916,12 +2921,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På högstubbe gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,21 +2937,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2963,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128191242</v>
+        <v>128191266</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,39 +2964,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571758</v>
+        <v>572072</v>
       </c>
       <c r="R21" t="n">
-        <v>7145043</v>
+        <v>7144777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3038,7 +3023,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3048,12 +3033,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På högstubbe gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,6 +3049,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191257</v>
+        <v>128191248</v>
       </c>
       <c r="B28" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,16 +3764,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3782,24 +3782,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571953</v>
+        <v>571940</v>
       </c>
       <c r="R28" t="n">
-        <v>7145103</v>
+        <v>7145031</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3831,7 +3828,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3841,12 +3838,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Spår efter födosökande</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,7 +3870,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191248</v>
+        <v>128191251</v>
       </c>
       <c r="B29" t="n">
         <v>57672</v>
@@ -3913,10 +3910,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571940</v>
+        <v>571965</v>
       </c>
       <c r="R29" t="n">
-        <v>7145031</v>
+        <v>7144858</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3948,7 +3945,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3958,12 +3955,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3990,10 +3987,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191251</v>
+        <v>128191263</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,39 +3998,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571965</v>
+        <v>571949</v>
       </c>
       <c r="R30" t="n">
-        <v>7144858</v>
+        <v>7144884</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,7 +4057,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4075,12 +4067,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4107,10 +4094,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191263</v>
+        <v>128191257</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,34 +4105,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571949</v>
+        <v>571953</v>
       </c>
       <c r="R31" t="n">
-        <v>7144884</v>
+        <v>7145103</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4177,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,7 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5300,61 +5300,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191256</v>
+        <v>128191275</v>
       </c>
       <c r="B41" t="n">
-        <v>98491</v>
+        <v>91370</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572118</v>
+        <v>571763</v>
       </c>
       <c r="R41" t="n">
-        <v>7144737</v>
+        <v>7145074</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5386,7 +5370,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5396,7 +5380,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5405,9 +5394,23 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5424,10 +5427,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191275</v>
+        <v>128191293</v>
       </c>
       <c r="B42" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5435,21 +5438,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5459,10 +5462,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571763</v>
+        <v>572031</v>
       </c>
       <c r="R42" t="n">
-        <v>7145074</v>
+        <v>7144794</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5494,7 +5497,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5504,12 +5507,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På högstubbe och lågan</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5520,21 +5518,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5551,7 +5534,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191293</v>
+        <v>128191290</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -5586,10 +5569,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572031</v>
+        <v>571947</v>
       </c>
       <c r="R43" t="n">
-        <v>7144794</v>
+        <v>7144803</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5621,7 +5604,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5631,7 +5614,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5658,10 +5646,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191290</v>
+        <v>128191245</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5669,34 +5657,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571947</v>
+        <v>571798</v>
       </c>
       <c r="R44" t="n">
-        <v>7144803</v>
+        <v>7145153</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5728,7 +5721,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5738,12 +5731,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5770,7 +5763,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191245</v>
+        <v>128191250</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5810,10 +5803,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571798</v>
+        <v>571954</v>
       </c>
       <c r="R45" t="n">
-        <v>7145153</v>
+        <v>7145092</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5845,7 +5838,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5855,12 +5848,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5887,50 +5880,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191250</v>
+        <v>128191256</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>98491</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571954</v>
+        <v>572118</v>
       </c>
       <c r="R46" t="n">
-        <v>7145092</v>
+        <v>7144737</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5962,7 +5966,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5972,12 +5976,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5986,6 +5985,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6462,10 +6462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191264</v>
+        <v>128191295</v>
       </c>
       <c r="B51" t="n">
-        <v>91348</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,21 +6473,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571949</v>
+        <v>572056</v>
       </c>
       <c r="R51" t="n">
-        <v>7144884</v>
+        <v>7144776</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6574,10 +6574,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128191295</v>
+        <v>128191264</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,21 +6585,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572056</v>
+        <v>571949</v>
       </c>
       <c r="R52" t="n">
-        <v>7144776</v>
+        <v>7144884</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,38 +925,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191235</v>
+        <v>128191284</v>
       </c>
       <c r="B4" t="n">
-        <v>92049</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
@@ -966,7 +963,7 @@
         <v>571958</v>
       </c>
       <c r="R4" t="n">
-        <v>7144868</v>
+        <v>7145094</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På högre stubbe</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,24 +1014,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,48 +1032,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191261</v>
+        <v>128191292</v>
       </c>
       <c r="B5" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572149</v>
+        <v>571980</v>
       </c>
       <c r="R5" t="n">
-        <v>7144695</v>
+        <v>7144787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,12 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,24 +1121,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1187,35 +1139,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191284</v>
+        <v>128191235</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>92049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
@@ -1225,7 +1180,7 @@
         <v>571958</v>
       </c>
       <c r="R6" t="n">
-        <v>7145094</v>
+        <v>7144868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1267,7 +1222,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,8 +1236,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1294,50 +1270,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191236</v>
+        <v>128191261</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>80168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571866</v>
+        <v>572149</v>
       </c>
       <c r="R7" t="n">
-        <v>7144903</v>
+        <v>7144695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,12 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,8 +1367,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1535,10 +1525,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191292</v>
+        <v>128191236</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,34 +1536,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571980</v>
+        <v>571866</v>
       </c>
       <c r="R9" t="n">
-        <v>7144787</v>
+        <v>7144903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191280</v>
+        <v>128191268</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571879</v>
+        <v>571872</v>
       </c>
       <c r="R23" t="n">
-        <v>7144984</v>
+        <v>7144850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,7 +3273,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,6 +3289,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3300,7 +3320,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191297</v>
+        <v>128191280</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -3335,10 +3355,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572085</v>
+        <v>571879</v>
       </c>
       <c r="R24" t="n">
-        <v>7144743</v>
+        <v>7144984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,7 +3390,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3380,7 +3400,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,7 +3427,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191277</v>
+        <v>128191297</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3442,10 +3462,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571951</v>
+        <v>572085</v>
       </c>
       <c r="R25" t="n">
-        <v>7144793</v>
+        <v>7144743</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,7 +3497,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,7 +3507,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191268</v>
+        <v>128191277</v>
       </c>
       <c r="B26" t="n">
-        <v>91348</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3525,21 +3545,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3549,10 +3569,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571872</v>
+        <v>571951</v>
       </c>
       <c r="R26" t="n">
-        <v>7144850</v>
+        <v>7144793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3584,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3594,12 +3614,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3610,21 +3625,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191248</v>
+        <v>128191257</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,16 +3764,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3782,21 +3782,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571940</v>
+        <v>571953</v>
       </c>
       <c r="R28" t="n">
-        <v>7145031</v>
+        <v>7145103</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3828,7 +3831,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3838,12 +3841,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,7 +3873,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191251</v>
+        <v>128191248</v>
       </c>
       <c r="B29" t="n">
         <v>57672</v>
@@ -3910,10 +3913,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571965</v>
+        <v>571940</v>
       </c>
       <c r="R29" t="n">
-        <v>7144858</v>
+        <v>7145031</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3945,7 +3948,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3955,12 +3958,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3987,10 +3990,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191263</v>
+        <v>128191251</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,34 +4001,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571949</v>
+        <v>571965</v>
       </c>
       <c r="R30" t="n">
-        <v>7144884</v>
+        <v>7144858</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4057,7 +4065,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4067,7 +4075,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,10 +4107,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191257</v>
+        <v>128191263</v>
       </c>
       <c r="B31" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4105,42 +4118,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571953</v>
+        <v>571949</v>
       </c>
       <c r="R31" t="n">
-        <v>7145103</v>
+        <v>7144884</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4187,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,27 +4214,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191262</v>
+        <v>128191238</v>
       </c>
       <c r="B32" t="n">
-        <v>57776</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4242,14 +4242,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4258,10 +4254,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571946</v>
+        <v>571774</v>
       </c>
       <c r="R32" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4293,7 +4289,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4303,12 +4299,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4335,7 +4331,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191238</v>
+        <v>128191243</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -4366,7 +4362,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4375,10 +4371,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571774</v>
+        <v>571776</v>
       </c>
       <c r="R33" t="n">
-        <v>7145037</v>
+        <v>7145163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4410,7 +4406,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4420,12 +4416,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4452,27 +4448,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191243</v>
+        <v>128191262</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>57776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4480,10 +4476,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571776</v>
+        <v>571946</v>
       </c>
       <c r="R34" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -6462,10 +6462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191295</v>
+        <v>128191264</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,21 +6473,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572056</v>
+        <v>571949</v>
       </c>
       <c r="R51" t="n">
-        <v>7144776</v>
+        <v>7144884</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6574,10 +6574,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128191264</v>
+        <v>128191295</v>
       </c>
       <c r="B52" t="n">
-        <v>91348</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,21 +6585,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571949</v>
+        <v>572056</v>
       </c>
       <c r="R52" t="n">
-        <v>7144884</v>
+        <v>7144776</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,35 +925,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191284</v>
+        <v>128191235</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>92049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
@@ -963,7 +966,7 @@
         <v>571958</v>
       </c>
       <c r="R4" t="n">
-        <v>7145094</v>
+        <v>7144868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,8 +1022,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1032,45 +1056,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191292</v>
+        <v>128191261</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571980</v>
+        <v>572149</v>
       </c>
       <c r="R5" t="n">
-        <v>7144787</v>
+        <v>7144695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1139,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,8 +1153,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1139,38 +1187,35 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191235</v>
+        <v>128191284</v>
       </c>
       <c r="B6" t="n">
-        <v>92049</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
@@ -1180,7 +1225,7 @@
         <v>571958</v>
       </c>
       <c r="R6" t="n">
-        <v>7144868</v>
+        <v>7145094</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1257,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,12 +1267,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På högre stubbe</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,24 +1276,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,48 +1294,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191261</v>
+        <v>128191236</v>
       </c>
       <c r="B7" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572149</v>
+        <v>571866</v>
       </c>
       <c r="R7" t="n">
-        <v>7144695</v>
+        <v>7144903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1379,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,24 +1393,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1525,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191236</v>
+        <v>128191292</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,39 +1546,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571866</v>
+        <v>571980</v>
       </c>
       <c r="R9" t="n">
-        <v>7144903</v>
+        <v>7144787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128191242</v>
+        <v>128191266</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,39 +2847,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571758</v>
+        <v>572072</v>
       </c>
       <c r="R20" t="n">
-        <v>7145043</v>
+        <v>7144777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2911,7 +2906,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,12 +2916,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På högstubbe gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,6 +2932,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2953,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128191266</v>
+        <v>128191242</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,34 +2974,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572072</v>
+        <v>571758</v>
       </c>
       <c r="R21" t="n">
-        <v>7144777</v>
+        <v>7145043</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3023,7 +3038,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3033,12 +3048,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På högstubbe gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3049,21 +3064,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191268</v>
+        <v>128191280</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571872</v>
+        <v>571879</v>
       </c>
       <c r="R23" t="n">
-        <v>7144850</v>
+        <v>7144984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,12 +3273,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,21 +3284,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3320,7 +3300,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191280</v>
+        <v>128191297</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -3355,10 +3335,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571879</v>
+        <v>572085</v>
       </c>
       <c r="R24" t="n">
-        <v>7144984</v>
+        <v>7144743</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3390,7 +3370,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3400,7 +3380,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,7 +3407,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191297</v>
+        <v>128191277</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3462,10 +3442,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572085</v>
+        <v>571951</v>
       </c>
       <c r="R25" t="n">
-        <v>7144743</v>
+        <v>7144793</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3497,7 +3477,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3507,7 +3487,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191277</v>
+        <v>128191268</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3545,21 +3525,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3569,10 +3549,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571951</v>
+        <v>571872</v>
       </c>
       <c r="R26" t="n">
-        <v>7144793</v>
+        <v>7144850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,7 +3584,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3614,7 +3594,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3625,6 +3610,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -4214,27 +4214,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191238</v>
+        <v>128191262</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>57776</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4242,10 +4242,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4254,10 +4258,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571774</v>
+        <v>571946</v>
       </c>
       <c r="R32" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4289,7 +4293,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4299,12 +4303,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,7 +4335,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191243</v>
+        <v>128191238</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -4362,7 +4366,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4371,10 +4375,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571776</v>
+        <v>571774</v>
       </c>
       <c r="R33" t="n">
-        <v>7145163</v>
+        <v>7145037</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,7 +4410,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4416,12 +4420,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4448,27 +4452,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191262</v>
+        <v>128191243</v>
       </c>
       <c r="B34" t="n">
-        <v>57776</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4476,14 +4480,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571946</v>
+        <v>571776</v>
       </c>
       <c r="R34" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5300,45 +5300,61 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191275</v>
+        <v>128191256</v>
       </c>
       <c r="B41" t="n">
-        <v>91370</v>
+        <v>98491</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571763</v>
+        <v>572118</v>
       </c>
       <c r="R41" t="n">
-        <v>7145074</v>
+        <v>7144737</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5370,7 +5386,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5380,12 +5396,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På högstubbe och lågan</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5394,23 +5405,9 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5427,10 +5424,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191293</v>
+        <v>128191275</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5438,21 +5435,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5462,10 +5459,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572031</v>
+        <v>571763</v>
       </c>
       <c r="R42" t="n">
-        <v>7144794</v>
+        <v>7145074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5497,7 +5494,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5507,7 +5504,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5518,6 +5520,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5534,7 +5551,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191290</v>
+        <v>128191293</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -5569,10 +5586,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571947</v>
+        <v>572031</v>
       </c>
       <c r="R43" t="n">
-        <v>7144803</v>
+        <v>7144794</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5604,7 +5621,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5614,12 +5631,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5646,10 +5658,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191245</v>
+        <v>128191290</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5657,39 +5669,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571798</v>
+        <v>571947</v>
       </c>
       <c r="R44" t="n">
-        <v>7145153</v>
+        <v>7144803</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5721,7 +5728,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5731,12 +5738,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5763,7 +5770,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191250</v>
+        <v>128191245</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5803,10 +5810,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571954</v>
+        <v>571798</v>
       </c>
       <c r="R45" t="n">
-        <v>7145092</v>
+        <v>7145153</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5838,7 +5845,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5848,12 +5855,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5880,61 +5887,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191256</v>
+        <v>128191250</v>
       </c>
       <c r="B46" t="n">
-        <v>98491</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572118</v>
+        <v>571954</v>
       </c>
       <c r="R46" t="n">
-        <v>7144737</v>
+        <v>7145092</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5966,7 +5962,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5976,7 +5972,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5985,7 +5986,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -1642,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128191254</v>
+        <v>128191288</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,39 +1653,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572189</v>
+        <v>571921</v>
       </c>
       <c r="R10" t="n">
-        <v>7144655</v>
+        <v>7144953</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1717,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1727,12 +1722,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,7 +1754,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128191288</v>
+        <v>128191298</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1794,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571921</v>
+        <v>572163</v>
       </c>
       <c r="R11" t="n">
-        <v>7144953</v>
+        <v>7144627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,12 +1834,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Riklig förekomst i större område</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128191298</v>
+        <v>128191254</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,34 +1877,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572163</v>
+        <v>572189</v>
       </c>
       <c r="R12" t="n">
-        <v>7144627</v>
+        <v>7144655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Riklig förekomst i större område</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128191266</v>
+        <v>128191242</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,34 +2847,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572072</v>
+        <v>571758</v>
       </c>
       <c r="R20" t="n">
-        <v>7144777</v>
+        <v>7145043</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2916,12 +2921,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På högstubbe gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,21 +2937,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2963,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128191242</v>
+        <v>128191266</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,39 +2964,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571758</v>
+        <v>572072</v>
       </c>
       <c r="R21" t="n">
-        <v>7145043</v>
+        <v>7144777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3038,7 +3023,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3048,12 +3033,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På högstubbe gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,6 +3049,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191257</v>
+        <v>128191248</v>
       </c>
       <c r="B28" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,16 +3764,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3782,24 +3782,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571953</v>
+        <v>571940</v>
       </c>
       <c r="R28" t="n">
-        <v>7145103</v>
+        <v>7145031</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3831,7 +3828,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3841,12 +3838,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Spår efter födosökande</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,7 +3870,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191248</v>
+        <v>128191251</v>
       </c>
       <c r="B29" t="n">
         <v>57672</v>
@@ -3913,10 +3910,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571940</v>
+        <v>571965</v>
       </c>
       <c r="R29" t="n">
-        <v>7145031</v>
+        <v>7144858</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3948,7 +3945,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3958,12 +3955,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3990,10 +3987,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191251</v>
+        <v>128191263</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,39 +3998,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571965</v>
+        <v>571949</v>
       </c>
       <c r="R30" t="n">
-        <v>7144858</v>
+        <v>7144884</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,7 +4057,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4075,12 +4067,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4107,10 +4094,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191263</v>
+        <v>128191257</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,34 +4105,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571949</v>
+        <v>571953</v>
       </c>
       <c r="R31" t="n">
-        <v>7144884</v>
+        <v>7145103</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4177,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,7 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5300,61 +5300,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191256</v>
+        <v>128191275</v>
       </c>
       <c r="B41" t="n">
-        <v>98491</v>
+        <v>91370</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572118</v>
+        <v>571763</v>
       </c>
       <c r="R41" t="n">
-        <v>7144737</v>
+        <v>7145074</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5386,7 +5370,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5396,7 +5380,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5405,9 +5394,23 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5424,10 +5427,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191275</v>
+        <v>128191293</v>
       </c>
       <c r="B42" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5435,21 +5438,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5459,10 +5462,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571763</v>
+        <v>572031</v>
       </c>
       <c r="R42" t="n">
-        <v>7145074</v>
+        <v>7144794</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5494,7 +5497,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5504,12 +5507,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På högstubbe och lågan</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5520,21 +5518,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5551,7 +5534,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191293</v>
+        <v>128191290</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -5586,10 +5569,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572031</v>
+        <v>571947</v>
       </c>
       <c r="R43" t="n">
-        <v>7144794</v>
+        <v>7144803</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5621,7 +5604,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5631,7 +5614,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5658,10 +5646,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191290</v>
+        <v>128191245</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5669,34 +5657,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571947</v>
+        <v>571798</v>
       </c>
       <c r="R44" t="n">
-        <v>7144803</v>
+        <v>7145153</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5728,7 +5721,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5738,12 +5731,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5770,7 +5763,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191245</v>
+        <v>128191250</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5810,10 +5803,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571798</v>
+        <v>571954</v>
       </c>
       <c r="R45" t="n">
-        <v>7145153</v>
+        <v>7145092</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5845,7 +5838,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5855,12 +5848,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5887,50 +5880,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191250</v>
+        <v>128191256</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>98491</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571954</v>
+        <v>572118</v>
       </c>
       <c r="R46" t="n">
-        <v>7145092</v>
+        <v>7144737</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5962,7 +5966,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5972,12 +5976,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5986,6 +5985,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6462,10 +6462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191264</v>
+        <v>128191295</v>
       </c>
       <c r="B51" t="n">
-        <v>91348</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,21 +6473,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571949</v>
+        <v>572056</v>
       </c>
       <c r="R51" t="n">
-        <v>7144884</v>
+        <v>7144776</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6574,10 +6574,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128191295</v>
+        <v>128191264</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>91348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,21 +6585,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572056</v>
+        <v>571949</v>
       </c>
       <c r="R52" t="n">
-        <v>7144776</v>
+        <v>7144884</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,48 +925,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191235</v>
+        <v>128191236</v>
       </c>
       <c r="B4" t="n">
-        <v>92049</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571958</v>
+        <v>571866</v>
       </c>
       <c r="R4" t="n">
-        <v>7144868</v>
+        <v>7144903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,24 +1024,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,37 +1042,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191261</v>
+        <v>128191255</v>
       </c>
       <c r="B5" t="n">
-        <v>80168</v>
+        <v>57833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1094,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572149</v>
+        <v>571834</v>
       </c>
       <c r="R5" t="n">
-        <v>7144695</v>
+        <v>7145195</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,12 +1134,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,24 +1148,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1187,45 +1166,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191284</v>
+        <v>128191261</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>80171</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571958</v>
+        <v>572149</v>
       </c>
       <c r="R6" t="n">
-        <v>7145094</v>
+        <v>7144695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1267,7 +1249,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,8 +1263,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1294,50 +1297,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191236</v>
+        <v>128191235</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>92057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571866</v>
+        <v>571958</v>
       </c>
       <c r="R7" t="n">
-        <v>7144903</v>
+        <v>7144868</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,12 +1380,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,8 +1394,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1411,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191255</v>
+        <v>128191292</v>
       </c>
       <c r="B8" t="n">
-        <v>57832</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,46 +1439,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571834</v>
+        <v>571980</v>
       </c>
       <c r="R8" t="n">
-        <v>7145195</v>
+        <v>7144787</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,7 +1498,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1503,12 +1508,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 st varnande</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191292</v>
+        <v>128191284</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571980</v>
+        <v>571958</v>
       </c>
       <c r="R9" t="n">
-        <v>7144787</v>
+        <v>7145094</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128191288</v>
+        <v>128191298</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571921</v>
+        <v>572163</v>
       </c>
       <c r="R10" t="n">
-        <v>7144953</v>
+        <v>7144627</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Riklig förekomst i större område</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1754,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128191298</v>
+        <v>128191288</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572163</v>
+        <v>571921</v>
       </c>
       <c r="R11" t="n">
-        <v>7144627</v>
+        <v>7144953</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig förekomst i större område</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,7 +1869,7 @@
         <v>128191254</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128191269</v>
       </c>
       <c r="B13" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128191253</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128191273</v>
       </c>
       <c r="B15" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191260</v>
+        <v>128191286</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,37 +2365,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572163</v>
+        <v>571922</v>
       </c>
       <c r="R16" t="n">
-        <v>7144677</v>
+        <v>7144993</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,12 +2434,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal levande sälg</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,24 +2443,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2485,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128191286</v>
+        <v>128191260</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>80135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,34 +2472,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571922</v>
+        <v>572163</v>
       </c>
       <c r="R17" t="n">
-        <v>7144993</v>
+        <v>7144677</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2555,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2565,7 +2544,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,8 +2558,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128191274</v>
+        <v>128191246</v>
       </c>
       <c r="B18" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,34 +2603,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571787</v>
+        <v>571764</v>
       </c>
       <c r="R18" t="n">
-        <v>7145163</v>
+        <v>7145073</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2667,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,12 +2677,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på låga</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2688,21 +2693,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2719,10 +2709,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128191246</v>
+        <v>128191274</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,39 +2720,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571764</v>
+        <v>571787</v>
       </c>
       <c r="R19" t="n">
-        <v>7145073</v>
+        <v>7145163</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2794,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2804,12 +2789,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla fruktkroppar på låga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,6 +2805,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2836,50 +2836,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128191242</v>
+        <v>128191258</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>97361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571758</v>
+        <v>571868</v>
       </c>
       <c r="R20" t="n">
-        <v>7145043</v>
+        <v>7144822</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2911,7 +2906,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,12 +2916,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Stort område med många plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,6 +2930,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2953,10 +2949,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128191266</v>
+        <v>128191242</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,34 +2960,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572072</v>
+        <v>571758</v>
       </c>
       <c r="R21" t="n">
-        <v>7144777</v>
+        <v>7145043</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3023,7 +3024,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3033,12 +3034,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På högstubbe gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3049,21 +3050,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3080,32 +3066,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128191258</v>
+        <v>128191266</v>
       </c>
       <c r="B22" t="n">
-        <v>97353</v>
+        <v>91356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3115,10 +3101,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571868</v>
+        <v>572072</v>
       </c>
       <c r="R22" t="n">
-        <v>7144822</v>
+        <v>7144777</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3150,7 +3136,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3160,12 +3146,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Stort område med många plantor</t>
+          <t>På högstubbe gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3174,9 +3160,23 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191280</v>
+        <v>128191268</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>91356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571879</v>
+        <v>571872</v>
       </c>
       <c r="R23" t="n">
-        <v>7144984</v>
+        <v>7144850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,7 +3273,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,6 +3289,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3300,10 +3320,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191297</v>
+        <v>128191280</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,10 +3355,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572085</v>
+        <v>571879</v>
       </c>
       <c r="R24" t="n">
-        <v>7144743</v>
+        <v>7144984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,7 +3390,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3380,7 +3400,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,10 +3427,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191277</v>
+        <v>128191297</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3442,10 +3462,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571951</v>
+        <v>572085</v>
       </c>
       <c r="R25" t="n">
-        <v>7144793</v>
+        <v>7144743</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,7 +3497,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,7 +3507,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191268</v>
+        <v>128191277</v>
       </c>
       <c r="B26" t="n">
-        <v>91348</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3525,21 +3545,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3549,10 +3569,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571872</v>
+        <v>571951</v>
       </c>
       <c r="R26" t="n">
-        <v>7144850</v>
+        <v>7144793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3584,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3594,12 +3614,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3610,21 +3625,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3644,7 +3644,7 @@
         <v>128191282</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191248</v>
+        <v>128191257</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>57670</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,16 +3764,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3782,21 +3782,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571940</v>
+        <v>571953</v>
       </c>
       <c r="R28" t="n">
-        <v>7145031</v>
+        <v>7145103</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3828,7 +3831,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3838,12 +3841,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,7 +3876,7 @@
         <v>128191251</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3987,10 +3990,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191263</v>
+        <v>128191248</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,34 +4001,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571949</v>
+        <v>571940</v>
       </c>
       <c r="R30" t="n">
-        <v>7144884</v>
+        <v>7145031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4057,7 +4065,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4067,7 +4075,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,10 +4107,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191257</v>
+        <v>128191263</v>
       </c>
       <c r="B31" t="n">
-        <v>57669</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4105,42 +4118,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571953</v>
+        <v>571949</v>
       </c>
       <c r="R31" t="n">
-        <v>7145103</v>
+        <v>7144884</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4187,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4217,7 +4217,7 @@
         <v>128191262</v>
       </c>
       <c r="B32" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191238</v>
+        <v>128191271</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,39 +4346,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571774</v>
+        <v>572031</v>
       </c>
       <c r="R33" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4410,7 +4405,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4420,12 +4415,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4436,6 +4431,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4452,10 +4462,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191243</v>
+        <v>128191238</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4493,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4492,10 +4502,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571776</v>
+        <v>571774</v>
       </c>
       <c r="R34" t="n">
-        <v>7145163</v>
+        <v>7145037</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4527,7 +4537,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4537,12 +4547,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4569,10 +4579,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191271</v>
+        <v>128191243</v>
       </c>
       <c r="B35" t="n">
-        <v>91348</v>
+        <v>57673</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4580,34 +4590,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572031</v>
+        <v>571776</v>
       </c>
       <c r="R35" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4639,7 +4654,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4649,12 +4664,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4665,21 +4680,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4699,7 +4699,7 @@
         <v>128191299</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>128191270</v>
       </c>
       <c r="B37" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>128191272</v>
       </c>
       <c r="B38" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128191265</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>128191259</v>
       </c>
       <c r="B40" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191275</v>
+        <v>128191245</v>
       </c>
       <c r="B41" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5311,34 +5311,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571763</v>
+        <v>571798</v>
       </c>
       <c r="R41" t="n">
-        <v>7145074</v>
+        <v>7145153</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5370,7 +5375,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5380,12 +5385,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På högstubbe och lågan</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5396,21 +5401,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5427,10 +5417,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191293</v>
+        <v>128191250</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5438,34 +5428,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572031</v>
+        <v>571954</v>
       </c>
       <c r="R42" t="n">
-        <v>7144794</v>
+        <v>7145092</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5497,7 +5492,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5507,7 +5502,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5534,45 +5534,61 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191290</v>
+        <v>128191256</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>98499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571947</v>
+        <v>572118</v>
       </c>
       <c r="R43" t="n">
-        <v>7144803</v>
+        <v>7144737</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5604,7 +5620,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5614,12 +5630,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5628,6 +5639,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5646,10 +5658,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191245</v>
+        <v>128191275</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5657,39 +5669,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571798</v>
+        <v>571763</v>
       </c>
       <c r="R44" t="n">
-        <v>7145153</v>
+        <v>7145074</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5721,7 +5728,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5731,12 +5738,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5747,6 +5754,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5763,10 +5785,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191250</v>
+        <v>128191290</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5774,39 +5796,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571954</v>
+        <v>571947</v>
       </c>
       <c r="R45" t="n">
-        <v>7145092</v>
+        <v>7144803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5838,7 +5855,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5848,12 +5865,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5880,61 +5897,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191256</v>
+        <v>128191293</v>
       </c>
       <c r="B46" t="n">
-        <v>98491</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572118</v>
+        <v>572031</v>
       </c>
       <c r="R46" t="n">
-        <v>7144737</v>
+        <v>7144794</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5966,7 +5967,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5976,7 +5977,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5985,7 +5986,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128191276</v>
+        <v>128191252</v>
       </c>
       <c r="B47" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6015,34 +6015,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572105</v>
+        <v>571967</v>
       </c>
       <c r="R47" t="n">
-        <v>7144753</v>
+        <v>7144855</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6074,7 +6079,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6084,12 +6089,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6100,21 +6105,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6131,10 +6121,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191285</v>
+        <v>128191276</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>91378</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6142,21 +6132,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6166,10 +6156,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571944</v>
+        <v>572105</v>
       </c>
       <c r="R48" t="n">
-        <v>7145060</v>
+        <v>7144753</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6201,7 +6191,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6211,7 +6201,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6222,6 +6217,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6241,7 +6251,7 @@
         <v>128191279</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6345,10 +6355,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128191252</v>
+        <v>128191285</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,39 +6366,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>571967</v>
+        <v>571944</v>
       </c>
       <c r="R50" t="n">
-        <v>7144855</v>
+        <v>7145060</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6420,7 +6425,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6430,12 +6435,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6462,10 +6462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191295</v>
+        <v>128191278</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572056</v>
+        <v>571873</v>
       </c>
       <c r="R51" t="n">
-        <v>7144776</v>
+        <v>7144925</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,12 +6542,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6577,7 +6572,7 @@
         <v>128191264</v>
       </c>
       <c r="B52" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6689,7 +6684,7 @@
         <v>128191296</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6793,10 +6788,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128191278</v>
+        <v>128191295</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6828,10 +6823,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571873</v>
+        <v>572056</v>
       </c>
       <c r="R54" t="n">
-        <v>7144925</v>
+        <v>7144776</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6863,7 +6858,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6873,7 +6868,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6903,7 +6903,7 @@
         <v>128191267</v>
       </c>
       <c r="B55" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7027,10 +7027,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128191289</v>
+        <v>128191249</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7038,34 +7038,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571956</v>
+        <v>571989</v>
       </c>
       <c r="R56" t="n">
-        <v>7144840</v>
+        <v>7145125</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7097,7 +7102,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7107,7 +7112,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7134,10 +7144,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128191281</v>
+        <v>128191247</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7145,34 +7155,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571939</v>
+        <v>571767</v>
       </c>
       <c r="R57" t="n">
-        <v>7145031</v>
+        <v>7145079</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7204,7 +7219,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7214,7 +7229,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7241,10 +7261,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128191249</v>
+        <v>128191241</v>
       </c>
       <c r="B58" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7272,7 +7292,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7281,10 +7301,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571989</v>
+        <v>571773</v>
       </c>
       <c r="R58" t="n">
-        <v>7145125</v>
+        <v>7145038</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7316,7 +7336,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7326,12 +7346,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7358,10 +7378,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128191241</v>
+        <v>128191289</v>
       </c>
       <c r="B59" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7369,39 +7389,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571773</v>
+        <v>571956</v>
       </c>
       <c r="R59" t="n">
-        <v>7145038</v>
+        <v>7144840</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7433,7 +7448,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7443,12 +7458,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7475,10 +7485,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128191247</v>
+        <v>128191281</v>
       </c>
       <c r="B60" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7486,39 +7496,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>571767</v>
+        <v>571939</v>
       </c>
       <c r="R60" t="n">
-        <v>7145079</v>
+        <v>7145031</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7550,7 +7555,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7560,12 +7565,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128191246</v>
+        <v>128191274</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>91378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,39 +2603,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571764</v>
+        <v>571787</v>
       </c>
       <c r="R18" t="n">
-        <v>7145073</v>
+        <v>7145163</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2667,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2677,12 +2672,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla fruktkroppar på låga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2693,6 +2688,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2709,10 +2719,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128191274</v>
+        <v>128191246</v>
       </c>
       <c r="B19" t="n">
-        <v>91378</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,34 +2730,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571787</v>
+        <v>571764</v>
       </c>
       <c r="R19" t="n">
-        <v>7145163</v>
+        <v>7145073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2794,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2804,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på låga</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,21 +2820,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191268</v>
+        <v>128191280</v>
       </c>
       <c r="B23" t="n">
-        <v>91356</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571872</v>
+        <v>571879</v>
       </c>
       <c r="R23" t="n">
-        <v>7144850</v>
+        <v>7144984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,12 +3273,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,21 +3284,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3320,7 +3300,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191280</v>
+        <v>128191297</v>
       </c>
       <c r="B24" t="n">
         <v>79032</v>
@@ -3355,10 +3335,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571879</v>
+        <v>572085</v>
       </c>
       <c r="R24" t="n">
-        <v>7144984</v>
+        <v>7144743</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3390,7 +3370,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3400,7 +3380,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,7 +3407,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191297</v>
+        <v>128191277</v>
       </c>
       <c r="B25" t="n">
         <v>79032</v>
@@ -3462,10 +3442,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572085</v>
+        <v>571951</v>
       </c>
       <c r="R25" t="n">
-        <v>7144743</v>
+        <v>7144793</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3497,7 +3477,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3507,7 +3487,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,7 +3514,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191277</v>
+        <v>128191282</v>
       </c>
       <c r="B26" t="n">
         <v>79032</v>
@@ -3569,10 +3549,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571951</v>
+        <v>571931</v>
       </c>
       <c r="R26" t="n">
-        <v>7144793</v>
+        <v>7145109</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,7 +3584,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3614,7 +3594,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,10 +3626,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128191282</v>
+        <v>128191268</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>91356</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3652,21 +3637,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3676,10 +3661,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571931</v>
+        <v>571872</v>
       </c>
       <c r="R27" t="n">
-        <v>7145109</v>
+        <v>7144850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3711,7 +3696,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,12 +3706,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3737,6 +3722,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191257</v>
+        <v>128191263</v>
       </c>
       <c r="B28" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,42 +3764,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571953</v>
+        <v>571949</v>
       </c>
       <c r="R28" t="n">
-        <v>7145103</v>
+        <v>7144884</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3831,7 +3823,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3841,12 +3833,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191251</v>
+        <v>128191257</v>
       </c>
       <c r="B29" t="n">
-        <v>57673</v>
+        <v>57670</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,16 +3871,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3902,21 +3889,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571965</v>
+        <v>571953</v>
       </c>
       <c r="R29" t="n">
-        <v>7144858</v>
+        <v>7145103</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3948,7 +3938,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3958,12 +3948,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3990,7 +3980,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191248</v>
+        <v>128191251</v>
       </c>
       <c r="B30" t="n">
         <v>57673</v>
@@ -4030,10 +4020,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571940</v>
+        <v>571965</v>
       </c>
       <c r="R30" t="n">
-        <v>7145031</v>
+        <v>7144858</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,7 +4055,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4075,12 +4065,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4107,10 +4097,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191263</v>
+        <v>128191248</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,34 +4108,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571949</v>
+        <v>571940</v>
       </c>
       <c r="R31" t="n">
-        <v>7144884</v>
+        <v>7145031</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4177,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,7 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,51 +4214,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191262</v>
+        <v>128191271</v>
       </c>
       <c r="B32" t="n">
-        <v>57777</v>
+        <v>91356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571946</v>
+        <v>572031</v>
       </c>
       <c r="R32" t="n">
         <v>7144801</v>
@@ -4293,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4303,12 +4294,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4319,6 +4310,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4335,10 +4341,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191271</v>
+        <v>128191238</v>
       </c>
       <c r="B33" t="n">
-        <v>91356</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,34 +4352,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572031</v>
+        <v>571774</v>
       </c>
       <c r="R33" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4405,7 +4416,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4415,12 +4426,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4431,21 +4442,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4462,7 +4458,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191238</v>
+        <v>128191243</v>
       </c>
       <c r="B34" t="n">
         <v>57673</v>
@@ -4493,7 +4489,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4502,10 +4498,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571774</v>
+        <v>571776</v>
       </c>
       <c r="R34" t="n">
-        <v>7145037</v>
+        <v>7145163</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4537,7 +4533,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4547,12 +4543,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4579,27 +4575,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191243</v>
+        <v>128191262</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>57777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4607,10 +4603,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571776</v>
+        <v>571946</v>
       </c>
       <c r="R35" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -6121,10 +6121,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191276</v>
+        <v>128191279</v>
       </c>
       <c r="B48" t="n">
-        <v>91378</v>
+        <v>79032</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,21 +6132,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572105</v>
+        <v>571825</v>
       </c>
       <c r="R48" t="n">
-        <v>7144753</v>
+        <v>7145166</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6201,12 +6201,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På högstubbe</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6217,21 +6212,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6248,7 +6228,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128191279</v>
+        <v>128191285</v>
       </c>
       <c r="B49" t="n">
         <v>79032</v>
@@ -6283,10 +6263,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571825</v>
+        <v>571944</v>
       </c>
       <c r="R49" t="n">
-        <v>7145166</v>
+        <v>7145060</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6318,7 +6298,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6328,7 +6308,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6355,10 +6335,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128191285</v>
+        <v>128191276</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>91378</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6366,21 +6346,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6390,10 +6370,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>571944</v>
+        <v>572105</v>
       </c>
       <c r="R50" t="n">
-        <v>7145060</v>
+        <v>7144753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6425,7 +6405,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6435,7 +6415,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6446,6 +6431,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191236</v>
+        <v>128191292</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,39 +936,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571866</v>
+        <v>571980</v>
       </c>
       <c r="R4" t="n">
-        <v>7144903</v>
+        <v>7144787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,12 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191255</v>
+        <v>128191284</v>
       </c>
       <c r="B5" t="n">
-        <v>57833</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,46 +1043,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571834</v>
+        <v>571958</v>
       </c>
       <c r="R5" t="n">
-        <v>7145195</v>
+        <v>7145094</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,12 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 st varnande</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1142,7 @@
         <v>128191261</v>
       </c>
       <c r="B6" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,37 +1270,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191235</v>
+        <v>128191255</v>
       </c>
       <c r="B7" t="n">
-        <v>92057</v>
+        <v>57845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1335,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571958</v>
+        <v>571834</v>
       </c>
       <c r="R7" t="n">
-        <v>7144868</v>
+        <v>7145195</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,12 +1362,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,24 +1376,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1428,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191292</v>
+        <v>128191236</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,34 +1405,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571980</v>
+        <v>571866</v>
       </c>
       <c r="R8" t="n">
-        <v>7144787</v>
+        <v>7144903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1498,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1508,7 +1479,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,35 +1511,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191284</v>
+        <v>128191235</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>92149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
@@ -1573,7 +1552,7 @@
         <v>571958</v>
       </c>
       <c r="R9" t="n">
-        <v>7145094</v>
+        <v>7144868</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,8 +1608,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1645,7 +1645,7 @@
         <v>128191298</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>128191288</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>128191254</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128191269</v>
       </c>
       <c r="B13" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128191253</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128191273</v>
       </c>
       <c r="B15" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191286</v>
+        <v>128191260</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,34 +2365,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571922</v>
+        <v>572163</v>
       </c>
       <c r="R16" t="n">
-        <v>7144993</v>
+        <v>7144677</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,7 +2437,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,8 +2451,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2461,10 +2485,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128191260</v>
+        <v>128191286</v>
       </c>
       <c r="B17" t="n">
-        <v>80135</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,37 +2496,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572163</v>
+        <v>571922</v>
       </c>
       <c r="R17" t="n">
-        <v>7144677</v>
+        <v>7144993</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2555,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,12 +2565,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal levande sälg</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,24 +2574,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2595,7 +2595,7 @@
         <v>128191274</v>
       </c>
       <c r="B18" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128191246</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>128191258</v>
       </c>
       <c r="B20" t="n">
-        <v>97361</v>
+        <v>97454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>128191242</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>128191266</v>
       </c>
       <c r="B22" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>128191280</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>128191297</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>128191277</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>128191282</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>128191268</v>
       </c>
       <c r="B27" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191263</v>
+        <v>128191257</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>57682</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,34 +3764,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571949</v>
+        <v>571953</v>
       </c>
       <c r="R28" t="n">
-        <v>7144884</v>
+        <v>7145103</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,7 +3831,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3841,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,10 +3873,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191257</v>
+        <v>128191263</v>
       </c>
       <c r="B29" t="n">
-        <v>57670</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3871,42 +3884,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571953</v>
+        <v>571949</v>
       </c>
       <c r="R29" t="n">
-        <v>7145103</v>
+        <v>7144884</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3938,7 +3943,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3948,12 +3953,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,10 +3980,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191251</v>
+        <v>128191248</v>
       </c>
       <c r="B30" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571965</v>
+        <v>571940</v>
       </c>
       <c r="R30" t="n">
-        <v>7144858</v>
+        <v>7145031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191248</v>
+        <v>128191251</v>
       </c>
       <c r="B31" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571940</v>
+        <v>571965</v>
       </c>
       <c r="R31" t="n">
-        <v>7145031</v>
+        <v>7144858</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4217,7 +4217,7 @@
         <v>128191271</v>
       </c>
       <c r="B32" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4341,27 +4341,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191238</v>
+        <v>128191262</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>57789</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4369,10 +4369,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4381,10 +4385,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571774</v>
+        <v>571946</v>
       </c>
       <c r="R33" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4416,7 +4420,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4426,12 +4430,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4458,10 +4462,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191243</v>
+        <v>128191238</v>
       </c>
       <c r="B34" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4489,7 +4493,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4498,10 +4502,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571776</v>
+        <v>571774</v>
       </c>
       <c r="R34" t="n">
-        <v>7145163</v>
+        <v>7145037</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4533,7 +4537,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4543,12 +4547,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4575,27 +4579,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191262</v>
+        <v>128191243</v>
       </c>
       <c r="B35" t="n">
-        <v>57777</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4603,14 +4607,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571946</v>
+        <v>571776</v>
       </c>
       <c r="R35" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4696,10 +4696,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128191299</v>
+        <v>128191270</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>91448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571913</v>
+        <v>571914</v>
       </c>
       <c r="R36" t="n">
-        <v>7145011</v>
+        <v>7144954</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe och lågan</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4792,6 +4792,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4808,10 +4823,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128191270</v>
+        <v>128191299</v>
       </c>
       <c r="B37" t="n">
-        <v>91356</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4819,21 +4834,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4843,10 +4858,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>571914</v>
+        <v>571913</v>
       </c>
       <c r="R37" t="n">
-        <v>7144954</v>
+        <v>7145011</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4878,7 +4893,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4888,12 +4903,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På stubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4904,21 +4919,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4938,7 +4938,7 @@
         <v>128191272</v>
       </c>
       <c r="B38" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128191265</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>128191259</v>
       </c>
       <c r="B40" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>128191245</v>
       </c>
       <c r="B41" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>128191250</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>128191256</v>
       </c>
       <c r="B43" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191275</v>
+        <v>128191290</v>
       </c>
       <c r="B44" t="n">
-        <v>91378</v>
+        <v>79083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5669,21 +5669,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571763</v>
+        <v>571947</v>
       </c>
       <c r="R44" t="n">
-        <v>7145074</v>
+        <v>7144803</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På högstubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5754,21 +5754,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5785,10 +5770,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191290</v>
+        <v>128191293</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5820,10 +5805,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571947</v>
+        <v>572031</v>
       </c>
       <c r="R45" t="n">
-        <v>7144803</v>
+        <v>7144794</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5855,7 +5840,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5865,12 +5850,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5897,10 +5877,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191293</v>
+        <v>128191275</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>91470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5908,21 +5888,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5932,10 +5912,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572031</v>
+        <v>571763</v>
       </c>
       <c r="R46" t="n">
-        <v>7144794</v>
+        <v>7145074</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5967,7 +5947,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5977,7 +5957,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5988,6 +5973,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6007,7 +6007,7 @@
         <v>128191252</v>
       </c>
       <c r="B47" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>128191279</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>128191285</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>128191276</v>
       </c>
       <c r="B50" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6462,10 +6462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191278</v>
+        <v>128191264</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>91448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,21 +6473,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571873</v>
+        <v>571949</v>
       </c>
       <c r="R51" t="n">
-        <v>7144925</v>
+        <v>7144884</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,7 +6542,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6569,10 +6574,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128191264</v>
+        <v>128191296</v>
       </c>
       <c r="B52" t="n">
-        <v>91356</v>
+        <v>79083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6580,21 +6585,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6604,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571949</v>
+        <v>572052</v>
       </c>
       <c r="R52" t="n">
-        <v>7144884</v>
+        <v>7144778</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6639,7 +6644,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6649,12 +6654,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På stubbe</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6681,10 +6681,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128191296</v>
+        <v>128191295</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572052</v>
+        <v>572056</v>
       </c>
       <c r="R53" t="n">
-        <v>7144778</v>
+        <v>7144776</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6761,7 +6761,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6788,10 +6793,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128191295</v>
+        <v>128191278</v>
       </c>
       <c r="B54" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6823,10 +6828,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572056</v>
+        <v>571873</v>
       </c>
       <c r="R54" t="n">
-        <v>7144776</v>
+        <v>7144925</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6858,7 +6863,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6868,12 +6873,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6900,10 +6900,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128191267</v>
+        <v>128191249</v>
       </c>
       <c r="B55" t="n">
-        <v>91356</v>
+        <v>57685</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6911,34 +6911,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572045</v>
+        <v>571989</v>
       </c>
       <c r="R55" t="n">
-        <v>7144778</v>
+        <v>7145125</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6970,7 +6975,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6980,12 +6985,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6996,21 +7001,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7027,10 +7017,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128191249</v>
+        <v>128191241</v>
       </c>
       <c r="B56" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7058,7 +7048,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7067,10 +7057,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571989</v>
+        <v>571773</v>
       </c>
       <c r="R56" t="n">
-        <v>7145125</v>
+        <v>7145038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7102,7 +7092,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7112,12 +7102,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7147,7 +7137,7 @@
         <v>128191247</v>
       </c>
       <c r="B57" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7261,10 +7251,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128191241</v>
+        <v>128191267</v>
       </c>
       <c r="B58" t="n">
-        <v>57673</v>
+        <v>91448</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7272,39 +7262,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571773</v>
+        <v>572045</v>
       </c>
       <c r="R58" t="n">
-        <v>7145038</v>
+        <v>7144778</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7336,7 +7321,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7346,12 +7331,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7362,6 +7347,21 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7381,7 +7381,7 @@
         <v>128191289</v>
       </c>
       <c r="B59" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>128191281</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,45 +925,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191292</v>
+        <v>128191235</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>92149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571980</v>
+        <v>571958</v>
       </c>
       <c r="R4" t="n">
-        <v>7144787</v>
+        <v>7144868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,8 +1022,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1032,7 +1056,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191284</v>
+        <v>128191292</v>
       </c>
       <c r="B5" t="n">
         <v>79083</v>
@@ -1067,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571958</v>
+        <v>571980</v>
       </c>
       <c r="R5" t="n">
-        <v>7145094</v>
+        <v>7144787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,48 +1163,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191261</v>
+        <v>128191284</v>
       </c>
       <c r="B6" t="n">
-        <v>80224</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572149</v>
+        <v>571958</v>
       </c>
       <c r="R6" t="n">
-        <v>7144695</v>
+        <v>7145094</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,12 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,24 +1252,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,46 +1270,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191255</v>
+        <v>128191261</v>
       </c>
       <c r="B7" t="n">
-        <v>57845</v>
+        <v>80224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1317,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571834</v>
+        <v>572149</v>
       </c>
       <c r="R7" t="n">
-        <v>7145195</v>
+        <v>7144695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,12 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 st varnande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,8 +1367,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1394,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191236</v>
+        <v>128191255</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>57845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,39 +1412,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571866</v>
+        <v>571834</v>
       </c>
       <c r="R8" t="n">
-        <v>7144903</v>
+        <v>7145195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,12 +1493,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,48 +1525,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191235</v>
+        <v>128191236</v>
       </c>
       <c r="B9" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571958</v>
+        <v>571866</v>
       </c>
       <c r="R9" t="n">
-        <v>7144868</v>
+        <v>7144903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,24 +1624,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128191298</v>
+        <v>128191254</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,34 +1653,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572163</v>
+        <v>572189</v>
       </c>
       <c r="R10" t="n">
-        <v>7144627</v>
+        <v>7144655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1717,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,12 +1727,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig förekomst i större område</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1754,7 +1759,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128191288</v>
+        <v>128191298</v>
       </c>
       <c r="B11" t="n">
         <v>79083</v>
@@ -1789,10 +1794,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571921</v>
+        <v>572163</v>
       </c>
       <c r="R11" t="n">
-        <v>7144953</v>
+        <v>7144627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1829,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,12 +1839,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Riklig förekomst i större område</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128191254</v>
+        <v>128191288</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,39 +1882,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572189</v>
+        <v>571921</v>
       </c>
       <c r="R12" t="n">
-        <v>7144655</v>
+        <v>7144953</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2836,32 +2836,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128191258</v>
+        <v>128191266</v>
       </c>
       <c r="B20" t="n">
-        <v>97454</v>
+        <v>91448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571868</v>
+        <v>572072</v>
       </c>
       <c r="R20" t="n">
-        <v>7144822</v>
+        <v>7144777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Stort område med många plantor</t>
+          <t>På högstubbe gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2930,9 +2930,23 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3066,32 +3080,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128191266</v>
+        <v>128191258</v>
       </c>
       <c r="B22" t="n">
-        <v>91448</v>
+        <v>97454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3101,10 +3115,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572072</v>
+        <v>571868</v>
       </c>
       <c r="R22" t="n">
-        <v>7144777</v>
+        <v>7144822</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3136,7 +3150,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3146,12 +3160,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På högstubbe gran</t>
+          <t>Stort område med många plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3160,23 +3174,9 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191280</v>
+        <v>128191268</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>91448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571879</v>
+        <v>571872</v>
       </c>
       <c r="R23" t="n">
-        <v>7144984</v>
+        <v>7144850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,7 +3273,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,6 +3289,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3300,7 +3320,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191297</v>
+        <v>128191280</v>
       </c>
       <c r="B24" t="n">
         <v>79083</v>
@@ -3335,10 +3355,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572085</v>
+        <v>571879</v>
       </c>
       <c r="R24" t="n">
-        <v>7144743</v>
+        <v>7144984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,7 +3390,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3380,7 +3400,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,7 +3427,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191277</v>
+        <v>128191297</v>
       </c>
       <c r="B25" t="n">
         <v>79083</v>
@@ -3442,10 +3462,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571951</v>
+        <v>572085</v>
       </c>
       <c r="R25" t="n">
-        <v>7144793</v>
+        <v>7144743</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,7 +3497,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,7 +3507,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,7 +3534,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191282</v>
+        <v>128191277</v>
       </c>
       <c r="B26" t="n">
         <v>79083</v>
@@ -3549,10 +3569,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571931</v>
+        <v>571951</v>
       </c>
       <c r="R26" t="n">
-        <v>7145109</v>
+        <v>7144793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3584,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3594,12 +3614,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3626,10 +3641,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128191268</v>
+        <v>128191282</v>
       </c>
       <c r="B27" t="n">
-        <v>91448</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3637,21 +3652,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3661,10 +3676,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571872</v>
+        <v>571931</v>
       </c>
       <c r="R27" t="n">
-        <v>7144850</v>
+        <v>7145109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3696,7 +3711,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3706,12 +3721,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På stubbe och låga</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3722,21 +3737,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3873,10 +3873,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191263</v>
+        <v>128191248</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,34 +3884,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571949</v>
+        <v>571940</v>
       </c>
       <c r="R29" t="n">
-        <v>7144884</v>
+        <v>7145031</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3943,7 +3948,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3953,7 +3958,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,7 +3990,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191248</v>
+        <v>128191251</v>
       </c>
       <c r="B30" t="n">
         <v>57685</v>
@@ -4020,10 +4030,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571940</v>
+        <v>571965</v>
       </c>
       <c r="R30" t="n">
-        <v>7145031</v>
+        <v>7144858</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4055,7 +4065,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4065,12 +4075,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,10 +4107,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191251</v>
+        <v>128191263</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4108,39 +4118,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571965</v>
+        <v>571949</v>
       </c>
       <c r="R31" t="n">
-        <v>7144858</v>
+        <v>7144884</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4187,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,10 +4214,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191271</v>
+        <v>128191238</v>
       </c>
       <c r="B32" t="n">
-        <v>91448</v>
+        <v>57685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,34 +4225,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572031</v>
+        <v>571774</v>
       </c>
       <c r="R32" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4284,7 +4289,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,12 +4299,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4310,21 +4315,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4341,27 +4331,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191262</v>
+        <v>128191243</v>
       </c>
       <c r="B33" t="n">
-        <v>57789</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4369,14 +4359,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4385,10 +4371,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571946</v>
+        <v>571776</v>
       </c>
       <c r="R33" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4420,7 +4406,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4430,12 +4416,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4462,10 +4448,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191238</v>
+        <v>128191271</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>91448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4473,39 +4459,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571774</v>
+        <v>572031</v>
       </c>
       <c r="R34" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4537,7 +4518,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4547,12 +4528,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4563,6 +4544,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4579,27 +4575,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191243</v>
+        <v>128191262</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>57789</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4607,10 +4603,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571776</v>
+        <v>571946</v>
       </c>
       <c r="R35" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5300,10 +5300,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191245</v>
+        <v>128191290</v>
       </c>
       <c r="B41" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5311,39 +5311,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571798</v>
+        <v>571947</v>
       </c>
       <c r="R41" t="n">
-        <v>7145153</v>
+        <v>7144803</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5375,7 +5370,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5385,12 +5380,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5417,10 +5412,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191250</v>
+        <v>128191293</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5428,39 +5423,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571954</v>
+        <v>572031</v>
       </c>
       <c r="R42" t="n">
-        <v>7145092</v>
+        <v>7144794</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5492,7 +5482,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5502,12 +5492,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5658,10 +5643,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191290</v>
+        <v>128191275</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5669,21 +5654,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5693,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571947</v>
+        <v>571763</v>
       </c>
       <c r="R44" t="n">
-        <v>7144803</v>
+        <v>7145074</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5728,7 +5713,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5738,12 +5723,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5754,6 +5739,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5770,10 +5770,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191293</v>
+        <v>128191245</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5781,34 +5781,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572031</v>
+        <v>571798</v>
       </c>
       <c r="R45" t="n">
-        <v>7144794</v>
+        <v>7145153</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5840,7 +5845,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5850,7 +5855,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5877,10 +5887,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191275</v>
+        <v>128191250</v>
       </c>
       <c r="B46" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5888,34 +5898,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571763</v>
+        <v>571954</v>
       </c>
       <c r="R46" t="n">
-        <v>7145074</v>
+        <v>7145092</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5947,7 +5962,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5957,12 +5972,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På högstubbe och lågan</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5973,21 +5988,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128191252</v>
+        <v>128191276</v>
       </c>
       <c r="B47" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6015,39 +6015,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>571967</v>
+        <v>572105</v>
       </c>
       <c r="R47" t="n">
-        <v>7144855</v>
+        <v>7144753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6079,7 +6074,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6089,12 +6084,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6105,6 +6100,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6335,10 +6345,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128191276</v>
+        <v>128191252</v>
       </c>
       <c r="B50" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6346,34 +6356,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572105</v>
+        <v>571967</v>
       </c>
       <c r="R50" t="n">
-        <v>7144753</v>
+        <v>7144855</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6405,7 +6420,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6415,12 +6430,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6431,21 +6446,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6900,10 +6900,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128191249</v>
+        <v>128191267</v>
       </c>
       <c r="B55" t="n">
-        <v>57685</v>
+        <v>91448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6911,39 +6911,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571989</v>
+        <v>572045</v>
       </c>
       <c r="R55" t="n">
-        <v>7145125</v>
+        <v>7144778</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6975,7 +6970,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6985,12 +6980,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7001,6 +6996,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7017,10 +7027,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128191241</v>
+        <v>128191289</v>
       </c>
       <c r="B56" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7028,39 +7038,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571773</v>
+        <v>571956</v>
       </c>
       <c r="R56" t="n">
-        <v>7145038</v>
+        <v>7144840</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7092,7 +7097,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7102,12 +7107,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7134,10 +7134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128191247</v>
+        <v>128191281</v>
       </c>
       <c r="B57" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7145,39 +7145,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571767</v>
+        <v>571939</v>
       </c>
       <c r="R57" t="n">
-        <v>7145079</v>
+        <v>7145031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7209,7 +7204,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7219,12 +7214,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7251,10 +7241,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128191267</v>
+        <v>128191241</v>
       </c>
       <c r="B58" t="n">
-        <v>91448</v>
+        <v>57685</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7262,34 +7252,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572045</v>
+        <v>571773</v>
       </c>
       <c r="R58" t="n">
-        <v>7144778</v>
+        <v>7145038</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7321,7 +7316,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7331,12 +7326,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7347,21 +7342,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7378,10 +7358,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128191289</v>
+        <v>128191247</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7389,34 +7369,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571956</v>
+        <v>571767</v>
       </c>
       <c r="R59" t="n">
-        <v>7144840</v>
+        <v>7145079</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7448,7 +7433,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7458,7 +7443,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7485,10 +7475,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128191281</v>
+        <v>128191249</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7496,34 +7486,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>571939</v>
+        <v>571989</v>
       </c>
       <c r="R60" t="n">
-        <v>7145031</v>
+        <v>7145125</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7555,7 +7550,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7565,7 +7560,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -1056,45 +1056,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191292</v>
+        <v>128191261</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>80224</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571980</v>
+        <v>572149</v>
       </c>
       <c r="R5" t="n">
-        <v>7144787</v>
+        <v>7144695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1139,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,8 +1153,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191284</v>
+        <v>128191236</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1198,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571958</v>
+        <v>571866</v>
       </c>
       <c r="R6" t="n">
-        <v>7145094</v>
+        <v>7144903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,48 +1304,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191261</v>
+        <v>128191292</v>
       </c>
       <c r="B7" t="n">
-        <v>80224</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572149</v>
+        <v>571980</v>
       </c>
       <c r="R7" t="n">
-        <v>7144695</v>
+        <v>7144787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1374,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1384,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,24 +1393,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1401,10 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191255</v>
+        <v>128191284</v>
       </c>
       <c r="B8" t="n">
-        <v>57845</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,46 +1422,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571834</v>
+        <v>571958</v>
       </c>
       <c r="R8" t="n">
-        <v>7145195</v>
+        <v>7145094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1493,12 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 st varnande</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191236</v>
+        <v>128191255</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>57845</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,39 +1529,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571866</v>
+        <v>571834</v>
       </c>
       <c r="R9" t="n">
-        <v>7144903</v>
+        <v>7145195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128191254</v>
+        <v>128191298</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,39 +1653,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572189</v>
+        <v>572163</v>
       </c>
       <c r="R10" t="n">
-        <v>7144655</v>
+        <v>7144627</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1717,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1727,12 +1722,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst i större område</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128191298</v>
+        <v>128191254</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,34 +1765,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572163</v>
+        <v>572189</v>
       </c>
       <c r="R11" t="n">
-        <v>7144627</v>
+        <v>7144655</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig förekomst i större område</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191260</v>
+        <v>128191286</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,37 +2365,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572163</v>
+        <v>571922</v>
       </c>
       <c r="R16" t="n">
-        <v>7144677</v>
+        <v>7144993</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,12 +2434,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal levande sälg</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,24 +2443,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2485,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128191286</v>
+        <v>128191260</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,34 +2472,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571922</v>
+        <v>572163</v>
       </c>
       <c r="R17" t="n">
-        <v>7144993</v>
+        <v>7144677</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2555,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2565,7 +2544,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,8 +2558,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191297</v>
+        <v>128191277</v>
       </c>
       <c r="B25" t="n">
         <v>79083</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572085</v>
+        <v>571951</v>
       </c>
       <c r="R25" t="n">
-        <v>7144743</v>
+        <v>7144793</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,7 +3534,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191277</v>
+        <v>128191282</v>
       </c>
       <c r="B26" t="n">
         <v>79083</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571951</v>
+        <v>571931</v>
       </c>
       <c r="R26" t="n">
-        <v>7144793</v>
+        <v>7145109</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3614,7 +3614,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,7 +3646,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128191282</v>
+        <v>128191297</v>
       </c>
       <c r="B27" t="n">
         <v>79083</v>
@@ -3676,10 +3681,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571931</v>
+        <v>572085</v>
       </c>
       <c r="R27" t="n">
-        <v>7145109</v>
+        <v>7144743</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3711,7 +3716,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,12 +3726,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191257</v>
+        <v>128191263</v>
       </c>
       <c r="B28" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,42 +3764,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571953</v>
+        <v>571949</v>
       </c>
       <c r="R28" t="n">
-        <v>7145103</v>
+        <v>7144884</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3831,7 +3823,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3841,12 +3833,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191248</v>
+        <v>128191257</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57682</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3884,16 +3871,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3902,21 +3889,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571940</v>
+        <v>571953</v>
       </c>
       <c r="R29" t="n">
-        <v>7145031</v>
+        <v>7145103</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3948,7 +3938,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3958,12 +3948,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3990,7 +3980,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191251</v>
+        <v>128191248</v>
       </c>
       <c r="B30" t="n">
         <v>57685</v>
@@ -4030,10 +4020,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571965</v>
+        <v>571940</v>
       </c>
       <c r="R30" t="n">
-        <v>7144858</v>
+        <v>7145031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,7 +4055,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4075,12 +4065,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4107,10 +4097,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191263</v>
+        <v>128191251</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,34 +4108,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571949</v>
+        <v>571965</v>
       </c>
       <c r="R31" t="n">
-        <v>7144884</v>
+        <v>7144858</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4177,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,7 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,10 +4214,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191238</v>
+        <v>128191271</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>91448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,39 +4225,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571774</v>
+        <v>572031</v>
       </c>
       <c r="R32" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4289,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4299,12 +4294,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4315,6 +4310,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4331,27 +4341,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191243</v>
+        <v>128191262</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>57789</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4359,10 +4369,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4371,10 +4385,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571776</v>
+        <v>571946</v>
       </c>
       <c r="R33" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,7 +4420,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4416,12 +4430,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4448,10 +4462,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191271</v>
+        <v>128191238</v>
       </c>
       <c r="B34" t="n">
-        <v>91448</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4459,34 +4473,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572031</v>
+        <v>571774</v>
       </c>
       <c r="R34" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4518,7 +4537,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4528,12 +4547,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4544,21 +4563,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4575,27 +4579,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191262</v>
+        <v>128191243</v>
       </c>
       <c r="B35" t="n">
-        <v>57789</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4603,14 +4607,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571946</v>
+        <v>571776</v>
       </c>
       <c r="R35" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5300,10 +5300,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191290</v>
+        <v>128191275</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5311,21 +5311,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571947</v>
+        <v>571763</v>
       </c>
       <c r="R41" t="n">
-        <v>7144803</v>
+        <v>7145074</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5396,6 +5396,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5412,7 +5427,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191293</v>
+        <v>128191290</v>
       </c>
       <c r="B42" t="n">
         <v>79083</v>
@@ -5447,10 +5462,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572031</v>
+        <v>571947</v>
       </c>
       <c r="R42" t="n">
-        <v>7144794</v>
+        <v>7144803</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5482,7 +5497,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5492,7 +5507,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5519,61 +5539,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191256</v>
+        <v>128191293</v>
       </c>
       <c r="B43" t="n">
-        <v>98592</v>
+        <v>79083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572118</v>
+        <v>572031</v>
       </c>
       <c r="R43" t="n">
-        <v>7144737</v>
+        <v>7144794</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5605,7 +5609,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5615,7 +5619,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5624,7 +5628,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5643,10 +5646,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191275</v>
+        <v>128191245</v>
       </c>
       <c r="B44" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5654,34 +5657,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571763</v>
+        <v>571798</v>
       </c>
       <c r="R44" t="n">
-        <v>7145074</v>
+        <v>7145153</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5713,7 +5721,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5723,12 +5731,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På högstubbe och lågan</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5739,21 +5747,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5770,7 +5763,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191245</v>
+        <v>128191250</v>
       </c>
       <c r="B45" t="n">
         <v>57685</v>
@@ -5810,10 +5803,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571798</v>
+        <v>571954</v>
       </c>
       <c r="R45" t="n">
-        <v>7145153</v>
+        <v>7145092</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5845,7 +5838,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5855,12 +5848,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5887,50 +5880,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191250</v>
+        <v>128191256</v>
       </c>
       <c r="B46" t="n">
-        <v>57685</v>
+        <v>98592</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571954</v>
+        <v>572118</v>
       </c>
       <c r="R46" t="n">
-        <v>7145092</v>
+        <v>7144737</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5962,7 +5966,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5972,12 +5976,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5986,6 +5985,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128191276</v>
+        <v>128191279</v>
       </c>
       <c r="B47" t="n">
-        <v>91470</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572105</v>
+        <v>571825</v>
       </c>
       <c r="R47" t="n">
-        <v>7144753</v>
+        <v>7145166</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6084,12 +6084,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På högstubbe</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6100,21 +6095,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6131,7 +6111,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191279</v>
+        <v>128191285</v>
       </c>
       <c r="B48" t="n">
         <v>79083</v>
@@ -6166,10 +6146,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571825</v>
+        <v>571944</v>
       </c>
       <c r="R48" t="n">
-        <v>7145166</v>
+        <v>7145060</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6201,7 +6181,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6211,7 +6191,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6238,10 +6218,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128191285</v>
+        <v>128191276</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6249,21 +6229,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6273,10 +6253,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571944</v>
+        <v>572105</v>
       </c>
       <c r="R49" t="n">
-        <v>7145060</v>
+        <v>7144753</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6308,7 +6288,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6318,7 +6298,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6329,6 +6314,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6681,7 +6681,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128191295</v>
+        <v>128191278</v>
       </c>
       <c r="B53" t="n">
         <v>79083</v>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572056</v>
+        <v>571873</v>
       </c>
       <c r="R53" t="n">
-        <v>7144776</v>
+        <v>7144925</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6761,12 +6761,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6793,7 +6788,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128191278</v>
+        <v>128191295</v>
       </c>
       <c r="B54" t="n">
         <v>79083</v>
@@ -6828,10 +6823,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571873</v>
+        <v>572056</v>
       </c>
       <c r="R54" t="n">
-        <v>7144925</v>
+        <v>7144776</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6863,7 +6858,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6873,7 +6868,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7241,7 +7241,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128191241</v>
+        <v>128191249</v>
       </c>
       <c r="B58" t="n">
         <v>57685</v>
@@ -7272,7 +7272,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571773</v>
+        <v>571989</v>
       </c>
       <c r="R58" t="n">
-        <v>7145038</v>
+        <v>7145125</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7358,7 +7358,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128191247</v>
+        <v>128191241</v>
       </c>
       <c r="B59" t="n">
         <v>57685</v>
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571767</v>
+        <v>571773</v>
       </c>
       <c r="R59" t="n">
-        <v>7145079</v>
+        <v>7145038</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7475,7 +7475,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128191249</v>
+        <v>128191247</v>
       </c>
       <c r="B60" t="n">
         <v>57685</v>
@@ -7506,7 +7506,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>571989</v>
+        <v>571767</v>
       </c>
       <c r="R60" t="n">
-        <v>7145125</v>
+        <v>7145079</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,48 +925,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191235</v>
+        <v>128191236</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571958</v>
+        <v>571866</v>
       </c>
       <c r="R4" t="n">
-        <v>7144868</v>
+        <v>7144903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,24 +1024,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191261</v>
+        <v>128191235</v>
       </c>
       <c r="B5" t="n">
-        <v>80224</v>
+        <v>92149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,21 +1053,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1094,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572149</v>
+        <v>571958</v>
       </c>
       <c r="R5" t="n">
-        <v>7144695</v>
+        <v>7144868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,17 +1145,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191236</v>
+        <v>128191292</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,39 +1184,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571866</v>
+        <v>571980</v>
       </c>
       <c r="R6" t="n">
-        <v>7144903</v>
+        <v>7144787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191292</v>
+        <v>128191284</v>
       </c>
       <c r="B7" t="n">
         <v>79083</v>
@@ -1339,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571980</v>
+        <v>571958</v>
       </c>
       <c r="R7" t="n">
-        <v>7144787</v>
+        <v>7145094</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1384,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,45 +1387,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191284</v>
+        <v>128191261</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>80224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571958</v>
+        <v>572149</v>
       </c>
       <c r="R8" t="n">
-        <v>7145094</v>
+        <v>7144695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,8 +1484,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191268</v>
+        <v>128191297</v>
       </c>
       <c r="B23" t="n">
-        <v>91448</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571872</v>
+        <v>572085</v>
       </c>
       <c r="R23" t="n">
-        <v>7144850</v>
+        <v>7144743</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,12 +3273,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,21 +3284,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3320,10 +3300,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191280</v>
+        <v>128191268</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>91448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,21 +3311,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3355,10 +3335,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571879</v>
+        <v>571872</v>
       </c>
       <c r="R24" t="n">
-        <v>7144984</v>
+        <v>7144850</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3390,7 +3370,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3400,7 +3380,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3411,6 +3396,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191277</v>
+        <v>128191280</v>
       </c>
       <c r="B25" t="n">
         <v>79083</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571951</v>
+        <v>571879</v>
       </c>
       <c r="R25" t="n">
-        <v>7144793</v>
+        <v>7144984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,7 +3534,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191282</v>
+        <v>128191277</v>
       </c>
       <c r="B26" t="n">
         <v>79083</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571931</v>
+        <v>571951</v>
       </c>
       <c r="R26" t="n">
-        <v>7145109</v>
+        <v>7144793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3614,12 +3614,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3646,7 +3641,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128191297</v>
+        <v>128191282</v>
       </c>
       <c r="B27" t="n">
         <v>79083</v>
@@ -3681,10 +3676,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572085</v>
+        <v>571931</v>
       </c>
       <c r="R27" t="n">
-        <v>7144743</v>
+        <v>7145109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3716,7 +3711,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3726,7 +3721,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4935,10 +4935,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128191272</v>
+        <v>128191265</v>
       </c>
       <c r="B38" t="n">
-        <v>91448</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4946,21 +4946,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572040</v>
+        <v>572072</v>
       </c>
       <c r="R38" t="n">
-        <v>7144775</v>
+        <v>7144777</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5015,12 +5015,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På högre stubbe och lågan</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5031,21 +5026,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5062,10 +5042,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128191265</v>
+        <v>128191272</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>91448</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5073,21 +5053,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5097,10 +5077,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572072</v>
+        <v>572040</v>
       </c>
       <c r="R39" t="n">
-        <v>7144777</v>
+        <v>7144775</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5132,7 +5112,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5142,7 +5122,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På högre stubbe och lågan</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5153,6 +5138,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191236</v>
+        <v>128191292</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,39 +936,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571866</v>
+        <v>571980</v>
       </c>
       <c r="R4" t="n">
-        <v>7144903</v>
+        <v>7144787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,12 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,38 +1032,35 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191235</v>
+        <v>128191284</v>
       </c>
       <c r="B5" t="n">
-        <v>92149</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
@@ -1083,7 +1070,7 @@
         <v>571958</v>
       </c>
       <c r="R5" t="n">
-        <v>7144868</v>
+        <v>7145094</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På högre stubbe</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,24 +1121,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,45 +1139,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191292</v>
+        <v>128191261</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>80228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571980</v>
+        <v>572149</v>
       </c>
       <c r="R6" t="n">
-        <v>7144787</v>
+        <v>7144695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1222,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,8 +1236,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191284</v>
+        <v>128191236</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,34 +1281,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571958</v>
+        <v>571866</v>
       </c>
       <c r="R7" t="n">
-        <v>7145094</v>
+        <v>7144903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,37 +1387,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191261</v>
+        <v>128191255</v>
       </c>
       <c r="B8" t="n">
-        <v>80224</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1425,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572149</v>
+        <v>571834</v>
       </c>
       <c r="R8" t="n">
-        <v>7144695</v>
+        <v>7145195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1479,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,24 +1493,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1518,46 +1511,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191255</v>
+        <v>128191235</v>
       </c>
       <c r="B9" t="n">
-        <v>57845</v>
+        <v>92161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1565,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571834</v>
+        <v>571958</v>
       </c>
       <c r="R9" t="n">
-        <v>7145195</v>
+        <v>7144868</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 st varnande</t>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,8 +1608,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1645,7 +1645,7 @@
         <v>128191298</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128191254</v>
+        <v>128191288</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,39 +1765,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572189</v>
+        <v>571921</v>
       </c>
       <c r="R11" t="n">
-        <v>7144655</v>
+        <v>7144953</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,12 +1834,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128191288</v>
+        <v>128191254</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,34 +1877,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571921</v>
+        <v>572189</v>
       </c>
       <c r="R12" t="n">
-        <v>7144953</v>
+        <v>7144655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,7 +1986,7 @@
         <v>128191269</v>
       </c>
       <c r="B13" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128191253</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128191273</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191286</v>
+        <v>128191260</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>80192</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,34 +2365,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571922</v>
+        <v>572163</v>
       </c>
       <c r="R16" t="n">
-        <v>7144993</v>
+        <v>7144677</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,7 +2437,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,8 +2451,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2461,10 +2485,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128191260</v>
+        <v>128191286</v>
       </c>
       <c r="B17" t="n">
-        <v>80188</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,37 +2496,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572163</v>
+        <v>571922</v>
       </c>
       <c r="R17" t="n">
-        <v>7144677</v>
+        <v>7144993</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2555,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,12 +2565,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal levande sälg</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,24 +2574,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2595,7 +2595,7 @@
         <v>128191274</v>
       </c>
       <c r="B18" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128191246</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>128191266</v>
       </c>
       <c r="B20" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>128191242</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>128191258</v>
       </c>
       <c r="B22" t="n">
-        <v>97454</v>
+        <v>97466</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191297</v>
+        <v>128191268</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>91460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572085</v>
+        <v>571872</v>
       </c>
       <c r="R23" t="n">
-        <v>7144743</v>
+        <v>7144850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,7 +3273,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,6 +3289,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3300,10 +3320,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191268</v>
+        <v>128191280</v>
       </c>
       <c r="B24" t="n">
-        <v>91448</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,21 +3331,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3335,10 +3355,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571872</v>
+        <v>571879</v>
       </c>
       <c r="R24" t="n">
-        <v>7144850</v>
+        <v>7144984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,7 +3390,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3380,12 +3400,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3396,21 +3411,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3427,10 +3427,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191280</v>
+        <v>128191297</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571879</v>
+        <v>572085</v>
       </c>
       <c r="R25" t="n">
-        <v>7144984</v>
+        <v>7144743</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3537,7 +3537,7 @@
         <v>128191277</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>128191282</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191263</v>
+        <v>128191248</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,34 +3764,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571949</v>
+        <v>571940</v>
       </c>
       <c r="R28" t="n">
-        <v>7144884</v>
+        <v>7145031</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,7 +3828,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3838,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3863,7 +3873,7 @@
         <v>128191257</v>
       </c>
       <c r="B29" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3980,10 +3990,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191248</v>
+        <v>128191263</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3991,39 +4001,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571940</v>
+        <v>571949</v>
       </c>
       <c r="R30" t="n">
-        <v>7145031</v>
+        <v>7144884</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4055,7 +4060,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4065,12 +4070,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4100,7 +4100,7 @@
         <v>128191251</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4214,42 +4214,51 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191271</v>
+        <v>128191262</v>
       </c>
       <c r="B32" t="n">
-        <v>91448</v>
+        <v>57793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572031</v>
+        <v>571946</v>
       </c>
       <c r="R32" t="n">
         <v>7144801</v>
@@ -4284,7 +4293,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,12 +4303,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4310,21 +4319,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4341,51 +4335,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191262</v>
+        <v>128191271</v>
       </c>
       <c r="B33" t="n">
-        <v>57789</v>
+        <v>91460</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571946</v>
+        <v>572031</v>
       </c>
       <c r="R33" t="n">
         <v>7144801</v>
@@ -4420,7 +4405,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4430,12 +4415,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4446,6 +4431,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4465,7 +4465,7 @@
         <v>128191238</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>128191243</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>128191270</v>
       </c>
       <c r="B36" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>128191299</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4935,10 +4935,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128191265</v>
+        <v>128191272</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>91460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4946,21 +4946,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572072</v>
+        <v>572040</v>
       </c>
       <c r="R38" t="n">
-        <v>7144777</v>
+        <v>7144775</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5015,7 +5015,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På högre stubbe och lågan</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5026,6 +5031,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5042,10 +5062,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128191272</v>
+        <v>128191265</v>
       </c>
       <c r="B39" t="n">
-        <v>91448</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5053,21 +5073,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5077,10 +5097,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572040</v>
+        <v>572072</v>
       </c>
       <c r="R39" t="n">
-        <v>7144775</v>
+        <v>7144777</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5112,7 +5132,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5122,12 +5142,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På högre stubbe och lågan</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5138,21 +5153,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5172,7 +5172,7 @@
         <v>128191259</v>
       </c>
       <c r="B40" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5300,45 +5300,61 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191275</v>
+        <v>128191256</v>
       </c>
       <c r="B41" t="n">
-        <v>91470</v>
+        <v>98606</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571763</v>
+        <v>572118</v>
       </c>
       <c r="R41" t="n">
-        <v>7145074</v>
+        <v>7144737</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5370,7 +5386,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5380,12 +5396,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På högstubbe och lågan</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5394,23 +5405,9 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5427,10 +5424,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191290</v>
+        <v>128191275</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>91482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5438,21 +5435,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5462,10 +5459,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571947</v>
+        <v>571763</v>
       </c>
       <c r="R42" t="n">
-        <v>7144803</v>
+        <v>7145074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5497,7 +5494,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5507,12 +5504,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5523,6 +5520,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5539,10 +5551,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191293</v>
+        <v>128191245</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5550,34 +5562,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572031</v>
+        <v>571798</v>
       </c>
       <c r="R43" t="n">
-        <v>7144794</v>
+        <v>7145153</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5609,7 +5626,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5619,7 +5636,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5646,10 +5668,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191245</v>
+        <v>128191250</v>
       </c>
       <c r="B44" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571798</v>
+        <v>571954</v>
       </c>
       <c r="R44" t="n">
-        <v>7145153</v>
+        <v>7145092</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5721,7 +5743,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5731,12 +5753,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5763,10 +5785,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191250</v>
+        <v>128191290</v>
       </c>
       <c r="B45" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5774,39 +5796,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571954</v>
+        <v>571947</v>
       </c>
       <c r="R45" t="n">
-        <v>7145092</v>
+        <v>7144803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5838,7 +5855,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5848,12 +5865,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5880,61 +5897,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191256</v>
+        <v>128191293</v>
       </c>
       <c r="B46" t="n">
-        <v>98592</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572118</v>
+        <v>572031</v>
       </c>
       <c r="R46" t="n">
-        <v>7144737</v>
+        <v>7144794</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5966,7 +5967,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5976,7 +5977,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5985,7 +5986,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128191279</v>
+        <v>128191276</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>91482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>571825</v>
+        <v>572105</v>
       </c>
       <c r="R47" t="n">
-        <v>7145166</v>
+        <v>7144753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6084,7 +6084,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6095,6 +6100,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6111,10 +6131,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191285</v>
+        <v>128191279</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6146,10 +6166,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571944</v>
+        <v>571825</v>
       </c>
       <c r="R48" t="n">
-        <v>7145060</v>
+        <v>7145166</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6181,7 +6201,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6191,7 +6211,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6218,10 +6238,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128191276</v>
+        <v>128191285</v>
       </c>
       <c r="B49" t="n">
-        <v>91470</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6229,21 +6249,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6253,10 +6273,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572105</v>
+        <v>571944</v>
       </c>
       <c r="R49" t="n">
-        <v>7144753</v>
+        <v>7145060</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6288,7 +6308,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6298,12 +6318,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På högstubbe</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6314,21 +6329,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6348,7 +6348,7 @@
         <v>128191252</v>
       </c>
       <c r="B50" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>128191264</v>
       </c>
       <c r="B51" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>128191296</v>
       </c>
       <c r="B52" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128191278</v>
+        <v>128191295</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>571873</v>
+        <v>572056</v>
       </c>
       <c r="R53" t="n">
-        <v>7144925</v>
+        <v>7144776</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6761,7 +6761,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6788,10 +6793,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128191295</v>
+        <v>128191278</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6823,10 +6828,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572056</v>
+        <v>571873</v>
       </c>
       <c r="R54" t="n">
-        <v>7144776</v>
+        <v>7144925</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6858,7 +6863,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6868,12 +6873,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6903,7 +6903,7 @@
         <v>128191267</v>
       </c>
       <c r="B55" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7027,10 +7027,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128191289</v>
+        <v>128191249</v>
       </c>
       <c r="B56" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7038,34 +7038,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571956</v>
+        <v>571989</v>
       </c>
       <c r="R56" t="n">
-        <v>7144840</v>
+        <v>7145125</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7097,7 +7102,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7107,7 +7112,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7134,10 +7144,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128191281</v>
+        <v>128191241</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7145,34 +7155,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571939</v>
+        <v>571773</v>
       </c>
       <c r="R57" t="n">
-        <v>7145031</v>
+        <v>7145038</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7204,7 +7219,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7214,7 +7229,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7241,10 +7261,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128191249</v>
+        <v>128191247</v>
       </c>
       <c r="B58" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7272,7 +7292,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7281,10 +7301,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571989</v>
+        <v>571767</v>
       </c>
       <c r="R58" t="n">
-        <v>7145125</v>
+        <v>7145079</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7316,7 +7336,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7326,12 +7346,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7358,10 +7378,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128191241</v>
+        <v>128191289</v>
       </c>
       <c r="B59" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7369,39 +7389,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571773</v>
+        <v>571956</v>
       </c>
       <c r="R59" t="n">
-        <v>7145038</v>
+        <v>7144840</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7433,7 +7448,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7443,12 +7458,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7475,10 +7485,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128191247</v>
+        <v>128191281</v>
       </c>
       <c r="B60" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7486,39 +7496,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>571767</v>
+        <v>571939</v>
       </c>
       <c r="R60" t="n">
-        <v>7145079</v>
+        <v>7145031</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7550,7 +7555,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7560,12 +7565,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,45 +925,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191292</v>
+        <v>128191235</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>92161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571980</v>
+        <v>571958</v>
       </c>
       <c r="R4" t="n">
-        <v>7144787</v>
+        <v>7144868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,8 +1022,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1032,7 +1056,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191284</v>
+        <v>128191292</v>
       </c>
       <c r="B5" t="n">
         <v>79087</v>
@@ -1067,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571958</v>
+        <v>571980</v>
       </c>
       <c r="R5" t="n">
-        <v>7145094</v>
+        <v>7144787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,48 +1163,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191261</v>
+        <v>128191284</v>
       </c>
       <c r="B6" t="n">
-        <v>80228</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572149</v>
+        <v>571958</v>
       </c>
       <c r="R6" t="n">
-        <v>7144695</v>
+        <v>7145094</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,12 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,24 +1252,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,50 +1270,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191236</v>
+        <v>128191261</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>80228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571866</v>
+        <v>572149</v>
       </c>
       <c r="R7" t="n">
-        <v>7144903</v>
+        <v>7144695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,8 +1367,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1387,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191255</v>
+        <v>128191236</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,46 +1412,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571834</v>
+        <v>571866</v>
       </c>
       <c r="R8" t="n">
-        <v>7145195</v>
+        <v>7144903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,12 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 st varnande</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,37 +1518,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191235</v>
+        <v>128191255</v>
       </c>
       <c r="B9" t="n">
-        <v>92161</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1549,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571958</v>
+        <v>571834</v>
       </c>
       <c r="R9" t="n">
-        <v>7144868</v>
+        <v>7145195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,24 +1624,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191248</v>
+        <v>128191263</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,39 +3764,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571940</v>
+        <v>571949</v>
       </c>
       <c r="R28" t="n">
-        <v>7145031</v>
+        <v>7144884</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3828,7 +3823,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3838,12 +3833,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3990,10 +3980,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191263</v>
+        <v>128191248</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,34 +3991,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571949</v>
+        <v>571940</v>
       </c>
       <c r="R30" t="n">
-        <v>7144884</v>
+        <v>7145031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,7 +4055,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4070,7 +4065,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4214,51 +4214,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191262</v>
+        <v>128191271</v>
       </c>
       <c r="B32" t="n">
-        <v>57793</v>
+        <v>91460</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571946</v>
+        <v>572031</v>
       </c>
       <c r="R32" t="n">
         <v>7144801</v>
@@ -4293,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4303,12 +4294,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4319,6 +4310,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4335,10 +4341,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191271</v>
+        <v>128191238</v>
       </c>
       <c r="B33" t="n">
-        <v>91460</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,34 +4352,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572031</v>
+        <v>571774</v>
       </c>
       <c r="R33" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4405,7 +4416,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4415,12 +4426,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4431,21 +4442,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4462,7 +4458,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191238</v>
+        <v>128191243</v>
       </c>
       <c r="B34" t="n">
         <v>57689</v>
@@ -4493,7 +4489,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4502,10 +4498,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571774</v>
+        <v>571776</v>
       </c>
       <c r="R34" t="n">
-        <v>7145037</v>
+        <v>7145163</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4537,7 +4533,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4547,12 +4543,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4579,27 +4575,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191243</v>
+        <v>128191262</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>57793</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4607,10 +4603,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571776</v>
+        <v>571946</v>
       </c>
       <c r="R35" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4935,10 +4935,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128191272</v>
+        <v>128191265</v>
       </c>
       <c r="B38" t="n">
-        <v>91460</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4946,21 +4946,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572040</v>
+        <v>572072</v>
       </c>
       <c r="R38" t="n">
-        <v>7144775</v>
+        <v>7144777</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5015,12 +5015,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På högre stubbe och lågan</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5031,21 +5026,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5062,10 +5042,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128191265</v>
+        <v>128191272</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>91460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5073,21 +5053,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5097,10 +5077,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572072</v>
+        <v>572040</v>
       </c>
       <c r="R39" t="n">
-        <v>7144777</v>
+        <v>7144775</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5132,7 +5112,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5142,7 +5122,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På högre stubbe och lågan</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5153,6 +5138,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5300,61 +5300,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191256</v>
+        <v>128191275</v>
       </c>
       <c r="B41" t="n">
-        <v>98606</v>
+        <v>91482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572118</v>
+        <v>571763</v>
       </c>
       <c r="R41" t="n">
-        <v>7144737</v>
+        <v>7145074</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5386,7 +5370,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5396,7 +5380,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5405,9 +5394,23 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5424,10 +5427,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191275</v>
+        <v>128191290</v>
       </c>
       <c r="B42" t="n">
-        <v>91482</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5435,21 +5438,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5459,10 +5462,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571763</v>
+        <v>571947</v>
       </c>
       <c r="R42" t="n">
-        <v>7145074</v>
+        <v>7144803</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5494,7 +5497,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5504,12 +5507,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På högstubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5520,21 +5523,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5551,10 +5539,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191245</v>
+        <v>128191293</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5562,39 +5550,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571798</v>
+        <v>572031</v>
       </c>
       <c r="R43" t="n">
-        <v>7145153</v>
+        <v>7144794</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5626,7 +5609,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5636,12 +5619,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5668,7 +5646,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191250</v>
+        <v>128191245</v>
       </c>
       <c r="B44" t="n">
         <v>57689</v>
@@ -5708,10 +5686,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571954</v>
+        <v>571798</v>
       </c>
       <c r="R44" t="n">
-        <v>7145092</v>
+        <v>7145153</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5743,7 +5721,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5753,12 +5731,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5785,10 +5763,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191290</v>
+        <v>128191250</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5796,34 +5774,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571947</v>
+        <v>571954</v>
       </c>
       <c r="R45" t="n">
-        <v>7144803</v>
+        <v>7145092</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5855,7 +5838,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5865,12 +5848,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5897,45 +5880,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191293</v>
+        <v>128191256</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>98606</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572031</v>
+        <v>572118</v>
       </c>
       <c r="R46" t="n">
-        <v>7144794</v>
+        <v>7144737</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5967,7 +5966,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5977,7 +5976,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5986,6 +5985,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191279</v>
+        <v>128191252</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6142,34 +6142,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571825</v>
+        <v>571967</v>
       </c>
       <c r="R48" t="n">
-        <v>7145166</v>
+        <v>7144855</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6201,7 +6206,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6211,7 +6216,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6238,7 +6248,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128191285</v>
+        <v>128191279</v>
       </c>
       <c r="B49" t="n">
         <v>79087</v>
@@ -6273,10 +6283,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571944</v>
+        <v>571825</v>
       </c>
       <c r="R49" t="n">
-        <v>7145060</v>
+        <v>7145166</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6308,7 +6318,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6318,7 +6328,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6345,10 +6355,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128191252</v>
+        <v>128191285</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,39 +6366,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>571967</v>
+        <v>571944</v>
       </c>
       <c r="R50" t="n">
-        <v>7144855</v>
+        <v>7145060</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6420,7 +6425,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6430,12 +6435,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128191235</v>
       </c>
       <c r="B4" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>128191292</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>128191284</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128191261</v>
       </c>
       <c r="B7" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>128191298</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>128191288</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128191269</v>
       </c>
       <c r="B13" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128191273</v>
       </c>
       <c r="B15" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>128191260</v>
       </c>
       <c r="B16" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>128191286</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>128191274</v>
       </c>
       <c r="B18" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>128191266</v>
       </c>
       <c r="B20" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>128191258</v>
       </c>
       <c r="B22" t="n">
-        <v>97466</v>
+        <v>97468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>128191268</v>
       </c>
       <c r="B23" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>128191280</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128191297</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>128191277</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>128191282</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191263</v>
+        <v>128191248</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,34 +3764,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571949</v>
+        <v>571940</v>
       </c>
       <c r="R28" t="n">
-        <v>7144884</v>
+        <v>7145031</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,7 +3828,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3838,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,10 +3870,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191257</v>
+        <v>128191251</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3871,16 +3881,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3889,24 +3899,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571953</v>
+        <v>571965</v>
       </c>
       <c r="R29" t="n">
-        <v>7145103</v>
+        <v>7144858</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3938,7 +3945,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3948,12 +3955,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spår efter födosökande</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,10 +3987,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191248</v>
+        <v>128191263</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3991,39 +3998,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571940</v>
+        <v>571949</v>
       </c>
       <c r="R30" t="n">
-        <v>7145031</v>
+        <v>7144884</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4055,7 +4057,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4065,12 +4067,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,10 +4094,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191251</v>
+        <v>128191257</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4108,16 +4105,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4126,21 +4123,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571965</v>
+        <v>571953</v>
       </c>
       <c r="R31" t="n">
-        <v>7144858</v>
+        <v>7145103</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,10 +4214,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191271</v>
+        <v>128191238</v>
       </c>
       <c r="B32" t="n">
-        <v>91460</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,34 +4225,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572031</v>
+        <v>571774</v>
       </c>
       <c r="R32" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4284,7 +4289,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,12 +4299,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4310,21 +4315,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4341,7 +4331,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191238</v>
+        <v>128191243</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -4372,7 +4362,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4381,10 +4371,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571774</v>
+        <v>571776</v>
       </c>
       <c r="R33" t="n">
-        <v>7145037</v>
+        <v>7145163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4416,7 +4406,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4426,12 +4416,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4458,10 +4448,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191243</v>
+        <v>128191271</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>91462</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4469,39 +4459,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571776</v>
+        <v>572031</v>
       </c>
       <c r="R34" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4533,7 +4518,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4543,12 +4528,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4559,6 +4544,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4696,10 +4696,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128191270</v>
+        <v>128191299</v>
       </c>
       <c r="B36" t="n">
-        <v>91460</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571914</v>
+        <v>571913</v>
       </c>
       <c r="R36" t="n">
-        <v>7144954</v>
+        <v>7145011</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På stubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4792,21 +4792,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4823,10 +4808,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128191299</v>
+        <v>128191270</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>91462</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4834,21 +4819,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4858,10 +4843,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>571913</v>
+        <v>571914</v>
       </c>
       <c r="R37" t="n">
-        <v>7145011</v>
+        <v>7144954</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4893,7 +4878,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4903,12 +4888,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe och lågan</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4919,6 +4904,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4935,10 +4935,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128191265</v>
+        <v>128191272</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>91462</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4946,21 +4946,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572072</v>
+        <v>572040</v>
       </c>
       <c r="R38" t="n">
-        <v>7144777</v>
+        <v>7144775</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5015,7 +5015,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På högre stubbe och lågan</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5026,6 +5031,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5042,10 +5062,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128191272</v>
+        <v>128191265</v>
       </c>
       <c r="B39" t="n">
-        <v>91460</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5053,21 +5073,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5077,10 +5097,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572040</v>
+        <v>572072</v>
       </c>
       <c r="R39" t="n">
-        <v>7144775</v>
+        <v>7144777</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5112,7 +5132,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5122,12 +5142,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På högre stubbe och lågan</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5138,21 +5153,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5172,7 +5172,7 @@
         <v>128191259</v>
       </c>
       <c r="B40" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5300,45 +5300,61 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191275</v>
+        <v>128191256</v>
       </c>
       <c r="B41" t="n">
-        <v>91482</v>
+        <v>98609</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571763</v>
+        <v>572118</v>
       </c>
       <c r="R41" t="n">
-        <v>7145074</v>
+        <v>7144737</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5370,7 +5386,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5380,12 +5396,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På högstubbe och lågan</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5394,23 +5405,9 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5427,10 +5424,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191290</v>
+        <v>128191275</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>91484</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5438,21 +5435,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5462,10 +5459,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571947</v>
+        <v>571763</v>
       </c>
       <c r="R42" t="n">
-        <v>7144803</v>
+        <v>7145074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5497,7 +5494,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5507,12 +5504,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5523,6 +5520,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5539,10 +5551,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191293</v>
+        <v>128191245</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5550,34 +5562,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572031</v>
+        <v>571798</v>
       </c>
       <c r="R43" t="n">
-        <v>7144794</v>
+        <v>7145153</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5609,7 +5626,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5619,7 +5636,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5646,7 +5668,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191245</v>
+        <v>128191250</v>
       </c>
       <c r="B44" t="n">
         <v>57689</v>
@@ -5686,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571798</v>
+        <v>571954</v>
       </c>
       <c r="R44" t="n">
-        <v>7145153</v>
+        <v>7145092</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5721,7 +5743,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5731,12 +5753,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5763,10 +5785,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191250</v>
+        <v>128191290</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5774,39 +5796,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571954</v>
+        <v>571947</v>
       </c>
       <c r="R45" t="n">
-        <v>7145092</v>
+        <v>7144803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5838,7 +5855,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5848,12 +5865,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5880,61 +5897,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191256</v>
+        <v>128191293</v>
       </c>
       <c r="B46" t="n">
-        <v>98606</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572118</v>
+        <v>572031</v>
       </c>
       <c r="R46" t="n">
-        <v>7144737</v>
+        <v>7144794</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5966,7 +5967,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5976,7 +5977,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5985,7 +5986,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>128191276</v>
       </c>
       <c r="B47" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191252</v>
+        <v>128191279</v>
       </c>
       <c r="B48" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6142,39 +6142,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571967</v>
+        <v>571825</v>
       </c>
       <c r="R48" t="n">
-        <v>7144855</v>
+        <v>7145166</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6206,7 +6201,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6216,12 +6211,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6248,10 +6238,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128191279</v>
+        <v>128191285</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6283,10 +6273,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571825</v>
+        <v>571944</v>
       </c>
       <c r="R49" t="n">
-        <v>7145166</v>
+        <v>7145060</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6318,7 +6308,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6328,7 +6318,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6355,10 +6345,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128191285</v>
+        <v>128191252</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6366,34 +6356,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>571944</v>
+        <v>571967</v>
       </c>
       <c r="R50" t="n">
-        <v>7145060</v>
+        <v>7144855</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6425,7 +6420,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6435,7 +6430,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6465,7 +6465,7 @@
         <v>128191264</v>
       </c>
       <c r="B51" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>128191296</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>128191295</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>128191278</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>128191267</v>
       </c>
       <c r="B55" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7027,10 +7027,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128191249</v>
+        <v>128191289</v>
       </c>
       <c r="B56" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7038,39 +7038,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571989</v>
+        <v>571956</v>
       </c>
       <c r="R56" t="n">
-        <v>7145125</v>
+        <v>7144840</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7102,7 +7097,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7112,12 +7107,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7144,10 +7134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128191241</v>
+        <v>128191281</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7155,39 +7145,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571773</v>
+        <v>571939</v>
       </c>
       <c r="R57" t="n">
-        <v>7145038</v>
+        <v>7145031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7219,7 +7204,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7229,12 +7214,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7261,7 +7241,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128191247</v>
+        <v>128191249</v>
       </c>
       <c r="B58" t="n">
         <v>57689</v>
@@ -7292,7 +7272,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7301,10 +7281,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571767</v>
+        <v>571989</v>
       </c>
       <c r="R58" t="n">
-        <v>7145079</v>
+        <v>7145125</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7336,7 +7316,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7346,12 +7326,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7378,10 +7358,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128191289</v>
+        <v>128191241</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7389,34 +7369,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571956</v>
+        <v>571773</v>
       </c>
       <c r="R59" t="n">
-        <v>7144840</v>
+        <v>7145038</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7448,7 +7433,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7458,7 +7443,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7485,10 +7475,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128191281</v>
+        <v>128191247</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7496,34 +7486,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>571939</v>
+        <v>571767</v>
       </c>
       <c r="R60" t="n">
-        <v>7145031</v>
+        <v>7145079</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7555,7 +7550,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7565,7 +7560,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191235</v>
+        <v>128191261</v>
       </c>
       <c r="B4" t="n">
-        <v>92163</v>
+        <v>80230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,21 +936,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571958</v>
+        <v>572149</v>
       </c>
       <c r="R4" t="n">
-        <v>7144868</v>
+        <v>7144695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191292</v>
+        <v>128191236</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,34 +1067,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571980</v>
+        <v>571866</v>
       </c>
       <c r="R5" t="n">
-        <v>7144787</v>
+        <v>7144903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1141,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191284</v>
+        <v>128191255</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1184,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571958</v>
+        <v>571834</v>
       </c>
       <c r="R6" t="n">
-        <v>7145094</v>
+        <v>7145195</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1265,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,48 +1297,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191261</v>
+        <v>128191292</v>
       </c>
       <c r="B7" t="n">
-        <v>80230</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572149</v>
+        <v>571980</v>
       </c>
       <c r="R7" t="n">
-        <v>7144695</v>
+        <v>7144787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,24 +1386,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1401,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191236</v>
+        <v>128191284</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,39 +1415,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571866</v>
+        <v>571958</v>
       </c>
       <c r="R8" t="n">
-        <v>7144903</v>
+        <v>7145094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,46 +1511,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191255</v>
+        <v>128191235</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>92163</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1565,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571834</v>
+        <v>571958</v>
       </c>
       <c r="R9" t="n">
-        <v>7145195</v>
+        <v>7144868</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 st varnande</t>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,8 +1608,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191268</v>
+        <v>128191280</v>
       </c>
       <c r="B23" t="n">
-        <v>91462</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571872</v>
+        <v>571879</v>
       </c>
       <c r="R23" t="n">
-        <v>7144850</v>
+        <v>7144984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,12 +3273,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,21 +3284,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3320,7 +3300,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191280</v>
+        <v>128191297</v>
       </c>
       <c r="B24" t="n">
         <v>79089</v>
@@ -3355,10 +3335,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571879</v>
+        <v>572085</v>
       </c>
       <c r="R24" t="n">
-        <v>7144984</v>
+        <v>7144743</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3390,7 +3370,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3400,7 +3380,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,7 +3407,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191297</v>
+        <v>128191277</v>
       </c>
       <c r="B25" t="n">
         <v>79089</v>
@@ -3462,10 +3442,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572085</v>
+        <v>571951</v>
       </c>
       <c r="R25" t="n">
-        <v>7144743</v>
+        <v>7144793</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3497,7 +3477,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3507,7 +3487,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,7 +3514,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191277</v>
+        <v>128191282</v>
       </c>
       <c r="B26" t="n">
         <v>79089</v>
@@ -3569,10 +3549,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571951</v>
+        <v>571931</v>
       </c>
       <c r="R26" t="n">
-        <v>7144793</v>
+        <v>7145109</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,7 +3584,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3614,7 +3594,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,10 +3626,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128191282</v>
+        <v>128191268</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>91462</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3652,21 +3637,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3676,10 +3661,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571931</v>
+        <v>571872</v>
       </c>
       <c r="R27" t="n">
-        <v>7145109</v>
+        <v>7144850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3711,7 +3696,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,12 +3706,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3737,6 +3722,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3753,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191248</v>
+        <v>128191263</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,39 +3764,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571940</v>
+        <v>571949</v>
       </c>
       <c r="R28" t="n">
-        <v>7145031</v>
+        <v>7144884</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3828,7 +3823,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3838,12 +3833,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191251</v>
+        <v>128191257</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3881,16 +3871,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3899,21 +3889,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571965</v>
+        <v>571953</v>
       </c>
       <c r="R29" t="n">
-        <v>7144858</v>
+        <v>7145103</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3945,7 +3938,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3955,12 +3948,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3987,10 +3980,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191263</v>
+        <v>128191248</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,34 +3991,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571949</v>
+        <v>571940</v>
       </c>
       <c r="R30" t="n">
-        <v>7144884</v>
+        <v>7145031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4057,7 +4055,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4067,7 +4065,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,10 +4097,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191257</v>
+        <v>128191251</v>
       </c>
       <c r="B31" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4105,16 +4108,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4123,24 +4126,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571953</v>
+        <v>571965</v>
       </c>
       <c r="R31" t="n">
-        <v>7145103</v>
+        <v>7144858</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Spår efter födosökande</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,10 +4214,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191238</v>
+        <v>128191271</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>91462</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,39 +4225,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571774</v>
+        <v>572031</v>
       </c>
       <c r="R32" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4289,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4299,12 +4294,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4315,6 +4310,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4331,7 +4341,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191243</v>
+        <v>128191238</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -4362,7 +4372,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4371,10 +4381,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571776</v>
+        <v>571774</v>
       </c>
       <c r="R33" t="n">
-        <v>7145163</v>
+        <v>7145037</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,7 +4416,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4416,12 +4426,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4448,10 +4458,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191271</v>
+        <v>128191243</v>
       </c>
       <c r="B34" t="n">
-        <v>91462</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4459,34 +4469,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572031</v>
+        <v>571776</v>
       </c>
       <c r="R34" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4518,7 +4533,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4528,12 +4543,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4544,21 +4559,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -5300,61 +5300,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191256</v>
+        <v>128191275</v>
       </c>
       <c r="B41" t="n">
-        <v>98609</v>
+        <v>91484</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572118</v>
+        <v>571763</v>
       </c>
       <c r="R41" t="n">
-        <v>7144737</v>
+        <v>7145074</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5386,7 +5370,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5396,7 +5380,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På högstubbe och lågan</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5405,9 +5394,23 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5424,10 +5427,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191275</v>
+        <v>128191290</v>
       </c>
       <c r="B42" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5435,21 +5438,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5459,10 +5462,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571763</v>
+        <v>571947</v>
       </c>
       <c r="R42" t="n">
-        <v>7145074</v>
+        <v>7144803</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5494,7 +5497,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5504,12 +5507,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På högstubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5520,21 +5523,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5785,45 +5773,61 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191290</v>
+        <v>128191256</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>98612</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571947</v>
+        <v>572118</v>
       </c>
       <c r="R45" t="n">
-        <v>7144803</v>
+        <v>7144737</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5855,7 +5859,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5865,12 +5869,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5879,6 +5878,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128191276</v>
+        <v>128191279</v>
       </c>
       <c r="B47" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572105</v>
+        <v>571825</v>
       </c>
       <c r="R47" t="n">
-        <v>7144753</v>
+        <v>7145166</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6084,12 +6084,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På högstubbe</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6100,21 +6095,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6131,7 +6111,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191279</v>
+        <v>128191285</v>
       </c>
       <c r="B48" t="n">
         <v>79089</v>
@@ -6166,10 +6146,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571825</v>
+        <v>571944</v>
       </c>
       <c r="R48" t="n">
-        <v>7145166</v>
+        <v>7145060</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6201,7 +6181,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6211,7 +6191,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6238,10 +6218,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128191285</v>
+        <v>128191252</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6249,34 +6229,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571944</v>
+        <v>571967</v>
       </c>
       <c r="R49" t="n">
-        <v>7145060</v>
+        <v>7144855</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6308,7 +6293,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6318,7 +6303,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6345,10 +6335,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128191252</v>
+        <v>128191276</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,39 +6346,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>571967</v>
+        <v>572105</v>
       </c>
       <c r="R50" t="n">
-        <v>7144855</v>
+        <v>7144753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6420,7 +6405,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6430,12 +6415,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6446,6 +6431,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7027,10 +7027,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128191289</v>
+        <v>128191247</v>
       </c>
       <c r="B56" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7038,34 +7038,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571956</v>
+        <v>571767</v>
       </c>
       <c r="R56" t="n">
-        <v>7144840</v>
+        <v>7145079</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7097,7 +7102,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7107,7 +7112,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7134,7 +7144,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128191281</v>
+        <v>128191289</v>
       </c>
       <c r="B57" t="n">
         <v>79089</v>
@@ -7169,10 +7179,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571939</v>
+        <v>571956</v>
       </c>
       <c r="R57" t="n">
-        <v>7145031</v>
+        <v>7144840</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7204,7 +7214,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7214,7 +7224,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7241,10 +7251,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128191249</v>
+        <v>128191281</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7252,39 +7262,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571989</v>
+        <v>571939</v>
       </c>
       <c r="R58" t="n">
-        <v>7145125</v>
+        <v>7145031</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7316,7 +7321,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7326,12 +7331,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7358,7 +7358,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128191241</v>
+        <v>128191249</v>
       </c>
       <c r="B59" t="n">
         <v>57689</v>
@@ -7389,7 +7389,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571773</v>
+        <v>571989</v>
       </c>
       <c r="R59" t="n">
-        <v>7145038</v>
+        <v>7145125</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7475,7 +7475,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128191247</v>
+        <v>128191241</v>
       </c>
       <c r="B60" t="n">
         <v>57689</v>
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>571767</v>
+        <v>571773</v>
       </c>
       <c r="R60" t="n">
-        <v>7145079</v>
+        <v>7145038</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191260</v>
+        <v>128191286</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,37 +2365,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572163</v>
+        <v>571922</v>
       </c>
       <c r="R16" t="n">
-        <v>7144677</v>
+        <v>7144993</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,12 +2434,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal levande sälg</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,24 +2443,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2485,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128191286</v>
+        <v>128191260</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,34 +2472,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571922</v>
+        <v>572163</v>
       </c>
       <c r="R17" t="n">
-        <v>7144993</v>
+        <v>7144677</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2555,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2565,7 +2544,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,8 +2558,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -4214,10 +4214,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191271</v>
+        <v>128191238</v>
       </c>
       <c r="B32" t="n">
-        <v>91462</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4225,34 +4225,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572031</v>
+        <v>571774</v>
       </c>
       <c r="R32" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4284,7 +4289,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,12 +4299,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4310,21 +4315,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4341,7 +4331,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191238</v>
+        <v>128191243</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -4372,7 +4362,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4381,10 +4371,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571774</v>
+        <v>571776</v>
       </c>
       <c r="R33" t="n">
-        <v>7145037</v>
+        <v>7145163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4416,7 +4406,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4426,12 +4416,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4458,10 +4448,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191243</v>
+        <v>128191271</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>91462</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4469,39 +4459,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571776</v>
+        <v>572031</v>
       </c>
       <c r="R34" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4533,7 +4518,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4543,12 +4528,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4559,6 +4544,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4696,10 +4696,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128191299</v>
+        <v>128191270</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>91462</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571913</v>
+        <v>571914</v>
       </c>
       <c r="R36" t="n">
-        <v>7145011</v>
+        <v>7144954</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe och lågan</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4792,6 +4792,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4808,10 +4823,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128191270</v>
+        <v>128191299</v>
       </c>
       <c r="B37" t="n">
-        <v>91462</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4819,21 +4834,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4843,10 +4858,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>571914</v>
+        <v>571913</v>
       </c>
       <c r="R37" t="n">
-        <v>7144954</v>
+        <v>7145011</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4878,7 +4893,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4888,12 +4903,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På stubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4904,21 +4919,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128191279</v>
+        <v>128191276</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>91484</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>571825</v>
+        <v>572105</v>
       </c>
       <c r="R47" t="n">
-        <v>7145166</v>
+        <v>7144753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6084,7 +6084,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6095,6 +6100,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6111,7 +6131,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191285</v>
+        <v>128191279</v>
       </c>
       <c r="B48" t="n">
         <v>79089</v>
@@ -6146,10 +6166,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571944</v>
+        <v>571825</v>
       </c>
       <c r="R48" t="n">
-        <v>7145060</v>
+        <v>7145166</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6181,7 +6201,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6191,7 +6211,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6218,10 +6238,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128191252</v>
+        <v>128191285</v>
       </c>
       <c r="B49" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6229,39 +6249,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571967</v>
+        <v>571944</v>
       </c>
       <c r="R49" t="n">
-        <v>7144855</v>
+        <v>7145060</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6293,7 +6308,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6303,12 +6318,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6335,10 +6345,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128191276</v>
+        <v>128191252</v>
       </c>
       <c r="B50" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6346,34 +6356,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572105</v>
+        <v>571967</v>
       </c>
       <c r="R50" t="n">
-        <v>7144753</v>
+        <v>7144855</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6405,7 +6420,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6415,12 +6430,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6431,21 +6446,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191261</v>
+        <v>128191235</v>
       </c>
       <c r="B4" t="n">
-        <v>80230</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,21 +936,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572149</v>
+        <v>571958</v>
       </c>
       <c r="R4" t="n">
-        <v>7144695</v>
+        <v>7144868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,50 +1056,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191236</v>
+        <v>128191261</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>80230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571866</v>
+        <v>572149</v>
       </c>
       <c r="R5" t="n">
-        <v>7144903</v>
+        <v>7144695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,12 +1139,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,8 +1153,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191255</v>
+        <v>128191292</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,46 +1198,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571834</v>
+        <v>571980</v>
       </c>
       <c r="R6" t="n">
-        <v>7145195</v>
+        <v>7144787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,7 +1257,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,12 +1267,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 st varnande</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,7 +1294,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191292</v>
+        <v>128191284</v>
       </c>
       <c r="B7" t="n">
         <v>79089</v>
@@ -1332,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571980</v>
+        <v>571958</v>
       </c>
       <c r="R7" t="n">
-        <v>7144787</v>
+        <v>7145094</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191284</v>
+        <v>128191236</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,34 +1412,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571958</v>
+        <v>571866</v>
       </c>
       <c r="R8" t="n">
-        <v>7145094</v>
+        <v>7144903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,37 +1518,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191235</v>
+        <v>128191255</v>
       </c>
       <c r="B9" t="n">
-        <v>92163</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1549,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571958</v>
+        <v>571834</v>
       </c>
       <c r="R9" t="n">
-        <v>7144868</v>
+        <v>7145195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,24 +1624,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1986,7 +1986,7 @@
         <v>128191269</v>
       </c>
       <c r="B13" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128191273</v>
       </c>
       <c r="B15" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191286</v>
+        <v>128191260</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,34 +2365,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571922</v>
+        <v>572163</v>
       </c>
       <c r="R16" t="n">
-        <v>7144993</v>
+        <v>7144677</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,7 +2437,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,8 +2451,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2461,10 +2485,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128191260</v>
+        <v>128191286</v>
       </c>
       <c r="B17" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,37 +2496,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572163</v>
+        <v>571922</v>
       </c>
       <c r="R17" t="n">
-        <v>7144677</v>
+        <v>7144993</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2555,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,12 +2565,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal levande sälg</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,24 +2574,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2595,7 +2595,7 @@
         <v>128191274</v>
       </c>
       <c r="B18" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>128191266</v>
       </c>
       <c r="B20" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>128191258</v>
       </c>
       <c r="B22" t="n">
-        <v>97468</v>
+        <v>97469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191280</v>
+        <v>128191268</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>91463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571879</v>
+        <v>571872</v>
       </c>
       <c r="R23" t="n">
-        <v>7144984</v>
+        <v>7144850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,7 +3273,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,6 +3289,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3300,7 +3320,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191297</v>
+        <v>128191280</v>
       </c>
       <c r="B24" t="n">
         <v>79089</v>
@@ -3335,10 +3355,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572085</v>
+        <v>571879</v>
       </c>
       <c r="R24" t="n">
-        <v>7144743</v>
+        <v>7144984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,7 +3390,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3380,7 +3400,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,7 +3427,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191277</v>
+        <v>128191297</v>
       </c>
       <c r="B25" t="n">
         <v>79089</v>
@@ -3442,10 +3462,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571951</v>
+        <v>572085</v>
       </c>
       <c r="R25" t="n">
-        <v>7144793</v>
+        <v>7144743</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,7 +3497,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,7 +3507,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,7 +3534,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191282</v>
+        <v>128191277</v>
       </c>
       <c r="B26" t="n">
         <v>79089</v>
@@ -3549,10 +3569,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571931</v>
+        <v>571951</v>
       </c>
       <c r="R26" t="n">
-        <v>7145109</v>
+        <v>7144793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3584,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3594,12 +3614,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3626,10 +3641,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128191268</v>
+        <v>128191282</v>
       </c>
       <c r="B27" t="n">
-        <v>91462</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3637,21 +3652,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3661,10 +3676,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571872</v>
+        <v>571931</v>
       </c>
       <c r="R27" t="n">
-        <v>7144850</v>
+        <v>7145109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3696,7 +3711,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3706,12 +3721,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På stubbe och låga</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3722,21 +3737,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4214,27 +4214,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191238</v>
+        <v>128191262</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>57793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4242,10 +4242,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4254,10 +4258,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571774</v>
+        <v>571946</v>
       </c>
       <c r="R32" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4289,7 +4293,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4299,12 +4303,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,10 +4335,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191243</v>
+        <v>128191271</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>91463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4342,39 +4346,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571776</v>
+        <v>572031</v>
       </c>
       <c r="R33" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,7 +4405,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4416,12 +4415,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4432,6 +4431,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4448,10 +4462,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191271</v>
+        <v>128191238</v>
       </c>
       <c r="B34" t="n">
-        <v>91462</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4459,34 +4473,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572031</v>
+        <v>571774</v>
       </c>
       <c r="R34" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4518,7 +4537,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4528,12 +4547,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4544,21 +4563,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4575,27 +4579,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191262</v>
+        <v>128191243</v>
       </c>
       <c r="B35" t="n">
-        <v>57793</v>
+        <v>57689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4603,14 +4607,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571946</v>
+        <v>571776</v>
       </c>
       <c r="R35" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4699,7 +4699,7 @@
         <v>128191270</v>
       </c>
       <c r="B36" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>128191272</v>
       </c>
       <c r="B38" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>128191275</v>
       </c>
       <c r="B41" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5539,10 +5539,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191245</v>
+        <v>128191293</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5550,39 +5550,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571798</v>
+        <v>572031</v>
       </c>
       <c r="R43" t="n">
-        <v>7145153</v>
+        <v>7144794</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5614,7 +5609,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5624,12 +5619,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5656,50 +5646,61 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191250</v>
+        <v>128191256</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>98613</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571954</v>
+        <v>572118</v>
       </c>
       <c r="R44" t="n">
-        <v>7145092</v>
+        <v>7144737</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5731,7 +5732,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5741,12 +5742,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5755,6 +5751,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5773,61 +5770,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191256</v>
+        <v>128191245</v>
       </c>
       <c r="B45" t="n">
-        <v>98612</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572118</v>
+        <v>571798</v>
       </c>
       <c r="R45" t="n">
-        <v>7144737</v>
+        <v>7145153</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5859,7 +5845,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5869,7 +5855,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5878,7 +5869,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5897,10 +5887,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191293</v>
+        <v>128191250</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5908,34 +5898,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572031</v>
+        <v>571954</v>
       </c>
       <c r="R46" t="n">
-        <v>7144794</v>
+        <v>7145092</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5967,7 +5962,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5977,7 +5972,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6007,7 +6007,7 @@
         <v>128191276</v>
       </c>
       <c r="B47" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6462,10 +6462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191264</v>
+        <v>128191296</v>
       </c>
       <c r="B51" t="n">
-        <v>91462</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,21 +6473,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571949</v>
+        <v>572052</v>
       </c>
       <c r="R51" t="n">
-        <v>7144884</v>
+        <v>7144778</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,12 +6542,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På stubbe</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6574,7 +6569,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128191296</v>
+        <v>128191295</v>
       </c>
       <c r="B52" t="n">
         <v>79089</v>
@@ -6609,10 +6604,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572052</v>
+        <v>572056</v>
       </c>
       <c r="R52" t="n">
-        <v>7144778</v>
+        <v>7144776</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6644,7 +6639,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6654,7 +6649,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6681,7 +6681,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128191295</v>
+        <v>128191278</v>
       </c>
       <c r="B53" t="n">
         <v>79089</v>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572056</v>
+        <v>571873</v>
       </c>
       <c r="R53" t="n">
-        <v>7144776</v>
+        <v>7144925</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6761,12 +6761,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6793,10 +6788,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128191278</v>
+        <v>128191264</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>91463</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6804,21 +6799,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6828,10 +6823,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571873</v>
+        <v>571949</v>
       </c>
       <c r="R54" t="n">
-        <v>7144925</v>
+        <v>7144884</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6863,7 +6858,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6873,7 +6868,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6900,10 +6900,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128191267</v>
+        <v>128191249</v>
       </c>
       <c r="B55" t="n">
-        <v>91462</v>
+        <v>57689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6911,34 +6911,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572045</v>
+        <v>571989</v>
       </c>
       <c r="R55" t="n">
-        <v>7144778</v>
+        <v>7145125</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6970,7 +6975,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6980,12 +6985,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6996,21 +7001,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7027,7 +7017,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128191247</v>
+        <v>128191241</v>
       </c>
       <c r="B56" t="n">
         <v>57689</v>
@@ -7067,10 +7057,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571767</v>
+        <v>571773</v>
       </c>
       <c r="R56" t="n">
-        <v>7145079</v>
+        <v>7145038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7102,7 +7092,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7112,12 +7102,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7144,10 +7134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128191289</v>
+        <v>128191247</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7155,34 +7145,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571956</v>
+        <v>571767</v>
       </c>
       <c r="R57" t="n">
-        <v>7144840</v>
+        <v>7145079</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7214,7 +7209,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7224,7 +7219,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7251,10 +7251,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128191281</v>
+        <v>128191267</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>91463</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7262,21 +7262,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571939</v>
+        <v>572045</v>
       </c>
       <c r="R58" t="n">
-        <v>7145031</v>
+        <v>7144778</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7331,7 +7331,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7342,6 +7347,21 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7358,10 +7378,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128191249</v>
+        <v>128191289</v>
       </c>
       <c r="B59" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7369,39 +7389,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571989</v>
+        <v>571956</v>
       </c>
       <c r="R59" t="n">
-        <v>7145125</v>
+        <v>7144840</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7433,7 +7448,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7443,12 +7458,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7475,10 +7485,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128191241</v>
+        <v>128191281</v>
       </c>
       <c r="B60" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7486,39 +7496,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>571773</v>
+        <v>571939</v>
       </c>
       <c r="R60" t="n">
-        <v>7145038</v>
+        <v>7145031</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7550,7 +7555,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7560,12 +7565,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,48 +925,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191235</v>
+        <v>128191236</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571958</v>
+        <v>571866</v>
       </c>
       <c r="R4" t="n">
-        <v>7144868</v>
+        <v>7144903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,24 +1024,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,37 +1042,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191261</v>
+        <v>128191255</v>
       </c>
       <c r="B5" t="n">
-        <v>80230</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1094,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572149</v>
+        <v>571834</v>
       </c>
       <c r="R5" t="n">
-        <v>7144695</v>
+        <v>7145195</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,12 +1134,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,24 +1148,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1187,45 +1166,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191292</v>
+        <v>128191235</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571980</v>
+        <v>571958</v>
       </c>
       <c r="R6" t="n">
-        <v>7144787</v>
+        <v>7144868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1267,7 +1249,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,8 +1263,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1294,45 +1297,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191284</v>
+        <v>128191261</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>80230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571958</v>
+        <v>572149</v>
       </c>
       <c r="R7" t="n">
-        <v>7145094</v>
+        <v>7144695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1380,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,8 +1394,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1401,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191236</v>
+        <v>128191292</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,39 +1439,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571866</v>
+        <v>571980</v>
       </c>
       <c r="R8" t="n">
-        <v>7144903</v>
+        <v>7144787</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1498,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1508,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191255</v>
+        <v>128191284</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,46 +1546,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571834</v>
+        <v>571958</v>
       </c>
       <c r="R9" t="n">
-        <v>7145195</v>
+        <v>7145094</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 st varnande</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2836,32 +2836,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128191266</v>
+        <v>128191258</v>
       </c>
       <c r="B20" t="n">
-        <v>91463</v>
+        <v>97469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572072</v>
+        <v>571868</v>
       </c>
       <c r="R20" t="n">
-        <v>7144777</v>
+        <v>7144822</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På högstubbe gran</t>
+          <t>Stort område med många plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2930,23 +2930,9 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2963,10 +2949,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128191242</v>
+        <v>128191266</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>91463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,39 +2960,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571758</v>
+        <v>572072</v>
       </c>
       <c r="R21" t="n">
-        <v>7145043</v>
+        <v>7144777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3038,7 +3019,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3048,12 +3029,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På högstubbe gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,6 +3045,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3080,45 +3076,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128191258</v>
+        <v>128191242</v>
       </c>
       <c r="B22" t="n">
-        <v>97469</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571868</v>
+        <v>571758</v>
       </c>
       <c r="R22" t="n">
-        <v>7144822</v>
+        <v>7145043</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3150,7 +3151,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3160,12 +3161,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Stort område med många plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3174,7 +3175,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128191270</v>
+        <v>128191299</v>
       </c>
       <c r="B36" t="n">
-        <v>91463</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571914</v>
+        <v>571913</v>
       </c>
       <c r="R36" t="n">
-        <v>7144954</v>
+        <v>7145011</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På stubbe och lågan</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4792,21 +4792,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4823,10 +4808,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128191299</v>
+        <v>128191270</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>91463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4834,21 +4819,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4858,10 +4843,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>571913</v>
+        <v>571914</v>
       </c>
       <c r="R37" t="n">
-        <v>7145011</v>
+        <v>7144954</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4893,7 +4878,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4903,12 +4888,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe och lågan</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4919,6 +4904,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191236</v>
+        <v>128191255</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,39 +936,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571866</v>
+        <v>571834</v>
       </c>
       <c r="R4" t="n">
-        <v>7144903</v>
+        <v>7145195</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,46 +1049,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191255</v>
+        <v>128191235</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>92191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1089,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571834</v>
+        <v>571958</v>
       </c>
       <c r="R5" t="n">
-        <v>7145195</v>
+        <v>7144868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,12 +1132,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 st varnande</t>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,8 +1146,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1166,48 +1180,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191235</v>
+        <v>128191292</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571958</v>
+        <v>571980</v>
       </c>
       <c r="R6" t="n">
-        <v>7144868</v>
+        <v>7144787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,12 +1260,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På högre stubbe</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,24 +1269,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1297,48 +1287,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191261</v>
+        <v>128191284</v>
       </c>
       <c r="B7" t="n">
-        <v>80230</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572149</v>
+        <v>571958</v>
       </c>
       <c r="R7" t="n">
-        <v>7144695</v>
+        <v>7145094</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,12 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,24 +1376,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1428,45 +1394,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191292</v>
+        <v>128191261</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>80257</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571980</v>
+        <v>572149</v>
       </c>
       <c r="R8" t="n">
-        <v>7144787</v>
+        <v>7144695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1498,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1508,7 +1477,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,8 +1491,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1535,10 +1525,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191284</v>
+        <v>128191236</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,34 +1536,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571958</v>
+        <v>571866</v>
       </c>
       <c r="R9" t="n">
-        <v>7145094</v>
+        <v>7144903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,7 +1645,7 @@
         <v>128191298</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>128191288</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>128191254</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128191269</v>
       </c>
       <c r="B13" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128191253</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128191273</v>
       </c>
       <c r="B15" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191260</v>
+        <v>128191286</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,37 +2365,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572163</v>
+        <v>571922</v>
       </c>
       <c r="R16" t="n">
-        <v>7144677</v>
+        <v>7144993</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,12 +2434,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal levande sälg</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,24 +2443,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2485,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128191286</v>
+        <v>128191260</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>80221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,34 +2472,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571922</v>
+        <v>572163</v>
       </c>
       <c r="R17" t="n">
-        <v>7144993</v>
+        <v>7144677</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2555,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2565,7 +2544,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,8 +2558,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2595,7 +2595,7 @@
         <v>128191274</v>
       </c>
       <c r="B18" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128191246</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2836,32 +2836,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128191258</v>
+        <v>128191266</v>
       </c>
       <c r="B20" t="n">
-        <v>97469</v>
+        <v>91490</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571868</v>
+        <v>572072</v>
       </c>
       <c r="R20" t="n">
-        <v>7144822</v>
+        <v>7144777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Stort område med många plantor</t>
+          <t>På högstubbe gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2930,9 +2930,23 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2949,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128191266</v>
+        <v>128191242</v>
       </c>
       <c r="B21" t="n">
-        <v>91463</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,34 +2974,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572072</v>
+        <v>571758</v>
       </c>
       <c r="R21" t="n">
-        <v>7144777</v>
+        <v>7145043</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3019,7 +3038,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3029,12 +3048,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På högstubbe gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3045,21 +3064,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3076,50 +3080,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128191242</v>
+        <v>128191258</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>97496</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571758</v>
+        <v>571868</v>
       </c>
       <c r="R22" t="n">
-        <v>7145043</v>
+        <v>7144822</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3151,7 +3150,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3161,12 +3160,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Stort område med många plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3175,6 +3174,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>128191268</v>
       </c>
       <c r="B23" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>128191280</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128191297</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>128191277</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>128191282</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>128191263</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191257</v>
+        <v>128191248</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3871,16 +3871,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3889,24 +3889,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571953</v>
+        <v>571940</v>
       </c>
       <c r="R29" t="n">
-        <v>7145103</v>
+        <v>7145031</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3938,7 +3935,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3948,12 +3945,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spår efter födosökande</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,10 +3977,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191248</v>
+        <v>128191251</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4020,10 +4017,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571940</v>
+        <v>571965</v>
       </c>
       <c r="R30" t="n">
-        <v>7145031</v>
+        <v>7144858</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4055,7 +4052,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4065,12 +4062,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,10 +4094,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191251</v>
+        <v>128191257</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>57713</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4108,16 +4105,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4126,21 +4123,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571965</v>
+        <v>571953</v>
       </c>
       <c r="R31" t="n">
-        <v>7144858</v>
+        <v>7145103</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,27 +4214,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191262</v>
+        <v>128191238</v>
       </c>
       <c r="B32" t="n">
-        <v>57793</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4242,14 +4242,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4258,10 +4254,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571946</v>
+        <v>571774</v>
       </c>
       <c r="R32" t="n">
-        <v>7144801</v>
+        <v>7145037</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4293,7 +4289,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4303,12 +4299,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4335,10 +4331,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191271</v>
+        <v>128191243</v>
       </c>
       <c r="B33" t="n">
-        <v>91463</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,34 +4342,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572031</v>
+        <v>571776</v>
       </c>
       <c r="R33" t="n">
-        <v>7144801</v>
+        <v>7145163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4405,7 +4406,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4415,12 +4416,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4431,21 +4432,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4462,27 +4448,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191238</v>
+        <v>128191262</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>57820</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4490,10 +4476,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4502,10 +4492,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571774</v>
+        <v>571946</v>
       </c>
       <c r="R34" t="n">
-        <v>7145037</v>
+        <v>7144801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4537,7 +4527,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4547,12 +4537,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4579,10 +4569,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191243</v>
+        <v>128191271</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>91490</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4590,39 +4580,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571776</v>
+        <v>572031</v>
       </c>
       <c r="R35" t="n">
-        <v>7145163</v>
+        <v>7144801</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,7 +4639,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,12 +4649,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,6 +4665,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4699,7 +4699,7 @@
         <v>128191299</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>128191270</v>
       </c>
       <c r="B37" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>128191272</v>
       </c>
       <c r="B38" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128191265</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>128191259</v>
       </c>
       <c r="B40" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>128191275</v>
       </c>
       <c r="B41" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>128191290</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>128191293</v>
       </c>
       <c r="B43" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5646,61 +5646,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191256</v>
+        <v>128191245</v>
       </c>
       <c r="B44" t="n">
-        <v>98613</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572118</v>
+        <v>571798</v>
       </c>
       <c r="R44" t="n">
-        <v>7144737</v>
+        <v>7145153</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5732,7 +5721,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5742,7 +5731,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5751,7 +5745,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5770,10 +5763,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191245</v>
+        <v>128191250</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5810,10 +5803,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571798</v>
+        <v>571954</v>
       </c>
       <c r="R45" t="n">
-        <v>7145153</v>
+        <v>7145092</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5845,7 +5838,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5855,12 +5848,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5887,50 +5880,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191250</v>
+        <v>128191256</v>
       </c>
       <c r="B46" t="n">
-        <v>57689</v>
+        <v>98640</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571954</v>
+        <v>572118</v>
       </c>
       <c r="R46" t="n">
-        <v>7145092</v>
+        <v>7144737</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5962,7 +5966,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5972,12 +5976,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5986,6 +5985,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>128191276</v>
       </c>
       <c r="B47" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>128191279</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>128191285</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>128191252</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6462,10 +6462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191296</v>
+        <v>128191264</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>91490</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,21 +6473,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572052</v>
+        <v>571949</v>
       </c>
       <c r="R51" t="n">
-        <v>7144778</v>
+        <v>7144884</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,7 +6542,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6569,10 +6574,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128191295</v>
+        <v>128191296</v>
       </c>
       <c r="B52" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6604,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572056</v>
+        <v>572052</v>
       </c>
       <c r="R52" t="n">
-        <v>7144776</v>
+        <v>7144778</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6639,7 +6644,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6649,12 +6654,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6681,10 +6681,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128191278</v>
+        <v>128191295</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>571873</v>
+        <v>572056</v>
       </c>
       <c r="R53" t="n">
-        <v>7144925</v>
+        <v>7144776</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6761,7 +6761,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6788,10 +6793,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128191264</v>
+        <v>128191278</v>
       </c>
       <c r="B54" t="n">
-        <v>91463</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6799,21 +6804,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6823,10 +6828,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571949</v>
+        <v>571873</v>
       </c>
       <c r="R54" t="n">
-        <v>7144884</v>
+        <v>7144925</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6858,7 +6863,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6868,12 +6873,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På stubbe</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6900,10 +6900,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128191249</v>
+        <v>128191267</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>91490</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6911,39 +6911,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571989</v>
+        <v>572045</v>
       </c>
       <c r="R55" t="n">
-        <v>7145125</v>
+        <v>7144778</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6975,7 +6970,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6985,12 +6980,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7001,6 +6996,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7017,10 +7027,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128191241</v>
+        <v>128191249</v>
       </c>
       <c r="B56" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7048,7 +7058,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7057,10 +7067,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571773</v>
+        <v>571989</v>
       </c>
       <c r="R56" t="n">
-        <v>7145038</v>
+        <v>7145125</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7092,7 +7102,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7102,12 +7112,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7134,10 +7144,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128191247</v>
+        <v>128191241</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7174,10 +7184,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571767</v>
+        <v>571773</v>
       </c>
       <c r="R57" t="n">
-        <v>7145079</v>
+        <v>7145038</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7209,7 +7219,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7219,12 +7229,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7251,10 +7261,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128191267</v>
+        <v>128191247</v>
       </c>
       <c r="B58" t="n">
-        <v>91463</v>
+        <v>57716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7262,34 +7272,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572045</v>
+        <v>571767</v>
       </c>
       <c r="R58" t="n">
-        <v>7144778</v>
+        <v>7145079</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7321,7 +7336,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7331,12 +7346,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7347,21 +7362,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7381,7 +7381,7 @@
         <v>128191289</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>128191281</v>
       </c>
       <c r="B60" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62023109</v>
+        <v>128191264</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Morfarsmyran, Ås lm</t>
+          <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571933.5870681521</v>
+        <v>571949</v>
       </c>
       <c r="R2" t="n">
-        <v>7144909.234182104</v>
+        <v>7144884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-08-14</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-08-14</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,44 +771,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg, Sven Bengtsson</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62023108</v>
+        <v>128191266</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,34 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Morfarsmyran, Ås lm</t>
+          <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572037.8694981416</v>
+        <v>572072</v>
       </c>
       <c r="R3" t="n">
-        <v>7144745.662072828</v>
+        <v>7144777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-08-14</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-08-14</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På högstubbe gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,38 +884,40 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg, Sven Bengtsson</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128191255</v>
+        <v>128191267</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,46 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571834</v>
+        <v>572045</v>
       </c>
       <c r="R4" t="n">
-        <v>7145195</v>
+        <v>7144778</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1 st varnande</t>
+          <t>På högstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,6 +1010,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1049,48 +1041,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128191235</v>
+        <v>128191268</v>
       </c>
       <c r="B5" t="n">
-        <v>92191</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571958</v>
+        <v>571872</v>
       </c>
       <c r="R5" t="n">
-        <v>7144868</v>
+        <v>7144850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På högre stubbe</t>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,7 +1135,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1180,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128191292</v>
+        <v>128191269</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,21 +1179,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571980</v>
+        <v>571861</v>
       </c>
       <c r="R6" t="n">
-        <v>7144787</v>
+        <v>7144892</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,7 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,6 +1264,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1287,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128191284</v>
+        <v>128191270</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,21 +1306,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1322,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571958</v>
+        <v>571914</v>
       </c>
       <c r="R7" t="n">
-        <v>7145094</v>
+        <v>7144954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1375,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På stubbe och lågan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,6 +1391,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1394,48 +1422,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128191261</v>
+        <v>128191271</v>
       </c>
       <c r="B8" t="n">
-        <v>80257</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572149</v>
+        <v>572031</v>
       </c>
       <c r="R8" t="n">
-        <v>7144695</v>
+        <v>7144801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,12 +1502,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,23 +1516,22 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1525,10 +1549,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128191236</v>
+        <v>128191272</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,39 +1560,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571866</v>
+        <v>572040</v>
       </c>
       <c r="R9" t="n">
-        <v>7144903</v>
+        <v>7144775</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1619,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1629,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På högre stubbe och lågan</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,6 +1645,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1642,45 +1676,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128191298</v>
+        <v>128191235</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572163</v>
+        <v>571958</v>
       </c>
       <c r="R10" t="n">
-        <v>7144627</v>
+        <v>7144868</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1749,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,12 +1759,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig förekomst i större område</t>
+          <t>På högre stubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,8 +1773,24 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1754,14 +1807,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128191288</v>
+        <v>128191263</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1789,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571921</v>
+        <v>571949</v>
       </c>
       <c r="R11" t="n">
-        <v>7144953</v>
+        <v>7144884</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1877,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,12 +1887,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,50 +1914,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128191254</v>
+        <v>128191265</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572189</v>
+        <v>572072</v>
       </c>
       <c r="R12" t="n">
-        <v>7144655</v>
+        <v>7144777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1984,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1994,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,32 +2021,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128191269</v>
+        <v>128191277</v>
       </c>
       <c r="B13" t="n">
-        <v>91490</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2018,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571861</v>
+        <v>571951</v>
       </c>
       <c r="R13" t="n">
-        <v>7144892</v>
+        <v>7144793</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2091,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,12 +2101,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,21 +2112,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2110,50 +2128,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128191253</v>
+        <v>128191278</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572126</v>
+        <v>571873</v>
       </c>
       <c r="R14" t="n">
-        <v>7144714</v>
+        <v>7144925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,7 +2198,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2195,12 +2208,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på låga med bark</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2227,32 +2235,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128191273</v>
+        <v>128191279</v>
       </c>
       <c r="B15" t="n">
-        <v>91512</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2270,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571862</v>
+        <v>571825</v>
       </c>
       <c r="R15" t="n">
-        <v>7144828</v>
+        <v>7145166</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,7 +2305,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2307,12 +2315,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På nyligen fallen trädstam</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,21 +2326,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2354,14 +2342,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191286</v>
+        <v>128191280</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2389,10 +2377,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571922</v>
+        <v>571879</v>
       </c>
       <c r="R16" t="n">
-        <v>7144993</v>
+        <v>7144984</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,7 +2412,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,7 +2422,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2461,48 +2449,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128191260</v>
+        <v>128191281</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572163</v>
+        <v>571939</v>
       </c>
       <c r="R17" t="n">
-        <v>7144677</v>
+        <v>7145031</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2519,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,12 +2529,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal levande sälg</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,24 +2538,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2592,32 +2556,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128191274</v>
+        <v>128191282</v>
       </c>
       <c r="B18" t="n">
-        <v>91512</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2627,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571787</v>
+        <v>571931</v>
       </c>
       <c r="R18" t="n">
-        <v>7145163</v>
+        <v>7145109</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2626,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,12 +2636,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på låga</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2688,21 +2652,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2719,50 +2668,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128191246</v>
+        <v>128191283</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571764</v>
+        <v>571986</v>
       </c>
       <c r="R19" t="n">
-        <v>7145073</v>
+        <v>7145154</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2794,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2804,12 +2748,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2836,32 +2775,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128191266</v>
+        <v>128191284</v>
       </c>
       <c r="B20" t="n">
-        <v>91490</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2871,10 +2810,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572072</v>
+        <v>571958</v>
       </c>
       <c r="R20" t="n">
-        <v>7144777</v>
+        <v>7145094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2916,12 +2855,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På högstubbe gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,21 +2866,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2963,50 +2882,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128191242</v>
+        <v>128191285</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571758</v>
+        <v>571944</v>
       </c>
       <c r="R21" t="n">
-        <v>7145043</v>
+        <v>7145060</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3038,7 +2952,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3048,12 +2962,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3080,32 +2989,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128191258</v>
+        <v>128191286</v>
       </c>
       <c r="B22" t="n">
-        <v>97496</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3115,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571868</v>
+        <v>571922</v>
       </c>
       <c r="R22" t="n">
-        <v>7144822</v>
+        <v>7144993</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3150,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3160,12 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Stort område med många plantor</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3174,7 +3078,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3193,32 +3096,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128191268</v>
+        <v>128191288</v>
       </c>
       <c r="B23" t="n">
-        <v>91490</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3131,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571872</v>
+        <v>571921</v>
       </c>
       <c r="R23" t="n">
-        <v>7144850</v>
+        <v>7144953</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,12 +3176,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På stubbe och låga</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,21 +3192,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3320,14 +3208,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128191280</v>
+        <v>128191289</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3355,10 +3243,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571879</v>
+        <v>571956</v>
       </c>
       <c r="R24" t="n">
-        <v>7144984</v>
+        <v>7144840</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3390,7 +3278,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3400,7 +3288,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,14 +3315,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128191297</v>
+        <v>128191290</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3462,10 +3350,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572085</v>
+        <v>571947</v>
       </c>
       <c r="R25" t="n">
-        <v>7144743</v>
+        <v>7144803</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3497,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3507,7 +3395,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,14 +3427,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128191277</v>
+        <v>128191292</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3569,10 +3462,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571951</v>
+        <v>571980</v>
       </c>
       <c r="R26" t="n">
-        <v>7144793</v>
+        <v>7144787</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3614,7 +3507,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,14 +3534,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128191282</v>
+        <v>128191293</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3676,10 +3569,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571931</v>
+        <v>572031</v>
       </c>
       <c r="R27" t="n">
-        <v>7145109</v>
+        <v>7144794</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3711,7 +3604,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,12 +3614,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3753,14 +3641,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128191263</v>
+        <v>128191295</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3788,10 +3676,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571949</v>
+        <v>572056</v>
       </c>
       <c r="R28" t="n">
-        <v>7144884</v>
+        <v>7144776</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,7 +3711,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3721,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,50 +3753,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128191248</v>
+        <v>128191296</v>
       </c>
       <c r="B29" t="n">
-        <v>57716</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571940</v>
+        <v>572052</v>
       </c>
       <c r="R29" t="n">
-        <v>7145031</v>
+        <v>7144778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3935,7 +3823,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,12 +3833,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3977,50 +3860,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128191251</v>
+        <v>128191297</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571965</v>
+        <v>572085</v>
       </c>
       <c r="R30" t="n">
-        <v>7144858</v>
+        <v>7144743</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4052,7 +3930,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4062,12 +3940,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,53 +3967,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128191257</v>
+        <v>128191298</v>
       </c>
       <c r="B31" t="n">
-        <v>57713</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571953</v>
+        <v>572163</v>
       </c>
       <c r="R31" t="n">
-        <v>7145103</v>
+        <v>7144627</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4037,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,12 +4047,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Spår efter födosökande</t>
+          <t>Riklig förekomst i större område</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4214,50 +4079,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128191238</v>
+        <v>128191299</v>
       </c>
       <c r="B32" t="n">
-        <v>57716</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571774</v>
+        <v>571913</v>
       </c>
       <c r="R32" t="n">
-        <v>7145037</v>
+        <v>7145011</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4289,7 +4149,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4299,12 +4159,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,10 +4191,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128191243</v>
+        <v>128191260</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4342,39 +4202,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571776</v>
+        <v>572163</v>
       </c>
       <c r="R33" t="n">
-        <v>7145163</v>
+        <v>7144677</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,7 +4264,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4416,12 +4274,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4430,8 +4288,24 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4448,10 +4322,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128191262</v>
+        <v>128191259</v>
       </c>
       <c r="B34" t="n">
-        <v>57820</v>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4459,43 +4333,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571946</v>
+        <v>572163</v>
       </c>
       <c r="R34" t="n">
-        <v>7144801</v>
+        <v>7144677</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4527,7 +4395,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4537,12 +4405,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>4 st födosökande</t>
+          <t>På gammal levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4551,8 +4419,24 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4569,45 +4453,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128191271</v>
+        <v>128191261</v>
       </c>
       <c r="B35" t="n">
-        <v>91490</v>
+        <v>80468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572031</v>
+        <v>572149</v>
       </c>
       <c r="R35" t="n">
-        <v>7144801</v>
+        <v>7144695</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4639,7 +4526,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4649,12 +4536,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4663,22 +4550,23 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4696,45 +4584,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128191299</v>
+        <v>128191257</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571913</v>
+        <v>571953</v>
       </c>
       <c r="R36" t="n">
-        <v>7145011</v>
+        <v>7145103</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,7 +4662,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4776,12 +4672,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Spår efter födosökande</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4808,10 +4704,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128191270</v>
+        <v>128191236</v>
       </c>
       <c r="B37" t="n">
-        <v>91490</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4819,34 +4715,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>571914</v>
+        <v>571866</v>
       </c>
       <c r="R37" t="n">
-        <v>7144954</v>
+        <v>7144903</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4878,7 +4779,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4888,12 +4789,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På stubbe och lågan</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4904,21 +4805,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4935,10 +4821,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128191272</v>
+        <v>128191238</v>
       </c>
       <c r="B38" t="n">
-        <v>91490</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4946,34 +4832,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572040</v>
+        <v>571774</v>
       </c>
       <c r="R38" t="n">
-        <v>7144775</v>
+        <v>7145037</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5005,7 +4896,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5015,12 +4906,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På högre stubbe och lågan</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5031,21 +4922,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5062,10 +4938,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128191265</v>
+        <v>128191241</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5073,34 +4949,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572072</v>
+        <v>571773</v>
       </c>
       <c r="R39" t="n">
-        <v>7144777</v>
+        <v>7145038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5132,7 +5013,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5142,7 +5023,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5169,48 +5055,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128191259</v>
+        <v>128191242</v>
       </c>
       <c r="B40" t="n">
-        <v>80250</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572163</v>
+        <v>571758</v>
       </c>
       <c r="R40" t="n">
-        <v>7144677</v>
+        <v>7145043</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5242,7 +5130,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5252,12 +5140,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5266,24 +5154,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5300,10 +5172,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128191275</v>
+        <v>128191243</v>
       </c>
       <c r="B41" t="n">
-        <v>91512</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5311,34 +5183,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571763</v>
+        <v>571776</v>
       </c>
       <c r="R41" t="n">
-        <v>7145074</v>
+        <v>7145163</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5370,7 +5247,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5380,12 +5257,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På högstubbe och lågan</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5396,21 +5273,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5427,10 +5289,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128191290</v>
+        <v>128191245</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5438,34 +5300,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571947</v>
+        <v>571798</v>
       </c>
       <c r="R42" t="n">
-        <v>7144803</v>
+        <v>7145153</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5497,7 +5364,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5507,12 +5374,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5539,10 +5406,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128191293</v>
+        <v>128191246</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5550,34 +5417,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572031</v>
+        <v>571764</v>
       </c>
       <c r="R43" t="n">
-        <v>7144794</v>
+        <v>7145073</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5609,7 +5481,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5619,7 +5491,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5646,10 +5523,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128191245</v>
+        <v>128191247</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5677,7 +5554,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5686,10 +5563,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571798</v>
+        <v>571767</v>
       </c>
       <c r="R44" t="n">
-        <v>7145153</v>
+        <v>7145079</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5721,7 +5598,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5731,12 +5608,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5763,10 +5640,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128191250</v>
+        <v>128191248</v>
       </c>
       <c r="B45" t="n">
-        <v>57716</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5803,10 +5680,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571954</v>
+        <v>571940</v>
       </c>
       <c r="R45" t="n">
-        <v>7145092</v>
+        <v>7145031</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5838,7 +5715,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5848,12 +5725,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5880,61 +5757,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128191256</v>
+        <v>128191249</v>
       </c>
       <c r="B46" t="n">
-        <v>98640</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572118</v>
+        <v>571989</v>
       </c>
       <c r="R46" t="n">
-        <v>7144737</v>
+        <v>7145125</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5966,7 +5832,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5976,7 +5842,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5985,7 +5856,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6004,10 +5874,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128191276</v>
+        <v>128191250</v>
       </c>
       <c r="B47" t="n">
-        <v>91512</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6015,34 +5885,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572105</v>
+        <v>571954</v>
       </c>
       <c r="R47" t="n">
-        <v>7144753</v>
+        <v>7145092</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6074,7 +5949,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6084,12 +5959,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På högstubbe</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6100,21 +5975,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6131,10 +5991,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128191279</v>
+        <v>128191251</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6142,34 +6002,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571825</v>
+        <v>571965</v>
       </c>
       <c r="R48" t="n">
-        <v>7145166</v>
+        <v>7144858</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6201,7 +6066,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6211,7 +6076,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6238,10 +6108,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128191285</v>
+        <v>128191252</v>
       </c>
       <c r="B49" t="n">
-        <v>79116</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6249,34 +6119,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571944</v>
+        <v>571967</v>
       </c>
       <c r="R49" t="n">
-        <v>7145060</v>
+        <v>7144855</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6308,7 +6183,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6318,7 +6193,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6345,10 +6225,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128191252</v>
+        <v>128191253</v>
       </c>
       <c r="B50" t="n">
-        <v>57716</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6376,7 +6256,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6385,10 +6265,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>571967</v>
+        <v>572126</v>
       </c>
       <c r="R50" t="n">
-        <v>7144855</v>
+        <v>7144714</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6420,7 +6300,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6430,12 +6310,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack på låga med bark</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6462,10 +6342,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128191264</v>
+        <v>128191254</v>
       </c>
       <c r="B51" t="n">
-        <v>91490</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,34 +6353,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571949</v>
+        <v>572189</v>
       </c>
       <c r="R51" t="n">
-        <v>7144884</v>
+        <v>7144655</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6532,7 +6417,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6542,12 +6427,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6574,10 +6459,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128191296</v>
+        <v>128191255</v>
       </c>
       <c r="B52" t="n">
-        <v>79116</v>
+        <v>58114</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,34 +6470,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572052</v>
+        <v>571834</v>
       </c>
       <c r="R52" t="n">
-        <v>7144778</v>
+        <v>7145195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6644,7 +6541,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6654,7 +6551,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1 st varnande</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6681,10 +6583,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128191295</v>
+        <v>128191262</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>58057</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6692,34 +6594,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572056</v>
+        <v>571946</v>
       </c>
       <c r="R53" t="n">
-        <v>7144776</v>
+        <v>7144801</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6751,7 +6662,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6761,12 +6672,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>4 st födosökande</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6793,32 +6704,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128191278</v>
+        <v>128191258</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>97989</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6828,10 +6739,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571873</v>
+        <v>571868</v>
       </c>
       <c r="R54" t="n">
-        <v>7144925</v>
+        <v>7144822</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6863,7 +6774,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6873,7 +6784,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Stort område med många plantor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6882,6 +6798,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6900,45 +6817,61 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128191267</v>
+        <v>128191256</v>
       </c>
       <c r="B55" t="n">
-        <v>91490</v>
+        <v>99140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Norrån, Fjälltuna, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572045</v>
+        <v>572118</v>
       </c>
       <c r="R55" t="n">
-        <v>7144778</v>
+        <v>7144737</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6970,7 +6903,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6980,12 +6913,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På högstubbe</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6994,23 +6922,9 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7024,571 +6938,6 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>128191249</v>
-      </c>
-      <c r="B56" t="n">
-        <v>57716</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Norrån, Fjälltuna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>571989</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7145125</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>128191241</v>
-      </c>
-      <c r="B57" t="n">
-        <v>57716</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Norrån, Fjälltuna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>571773</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7145038</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>128191247</v>
-      </c>
-      <c r="B58" t="n">
-        <v>57716</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Norrån, Fjälltuna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>571767</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7145079</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>128191289</v>
-      </c>
-      <c r="B59" t="n">
-        <v>79116</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Norrån, Fjälltuna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>571956</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7144840</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>128191281</v>
-      </c>
-      <c r="B60" t="n">
-        <v>79116</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Norrån, Fjälltuna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>571939</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7145031</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25257-2025 artfynd.xlsx
+++ b/artfynd/A 25257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191264</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191266</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191267</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1165,6 +1185,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191268</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1292,6 +1317,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191269</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1419,6 +1449,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191270</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1546,6 +1581,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191271</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1673,6 +1713,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191272</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1804,6 +1849,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191235</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1911,6 +1961,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191263</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2018,6 +2073,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191265</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2125,6 +2185,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191277</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2232,6 +2297,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191278</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2339,6 +2409,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191279</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2446,6 +2521,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191280</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2553,6 +2633,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191281</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2665,6 +2750,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191282</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2772,6 +2862,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191283</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2879,6 +2974,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191284</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2986,6 +3086,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191285</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3093,6 +3198,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191286</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3205,6 +3315,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191288</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3312,6 +3427,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191289</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3424,6 +3544,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191290</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3531,6 +3656,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191292</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3638,6 +3768,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191293</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3750,6 +3885,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191295</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3857,6 +3997,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191296</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3964,6 +4109,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191297</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4076,6 +4226,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191298</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4188,6 +4343,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191299</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4319,6 +4479,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191260</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4450,6 +4615,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191259</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4581,6 +4751,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191261</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4701,6 +4876,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191257</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4818,6 +4998,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191236</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4935,6 +5120,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191238</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5052,6 +5242,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191241</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5169,6 +5364,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191242</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5286,6 +5486,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191243</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5403,6 +5608,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191245</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5520,6 +5730,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191246</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5637,6 +5852,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191247</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5754,6 +5974,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191248</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5871,6 +6096,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191249</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5988,6 +6218,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191250</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6105,6 +6340,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191251</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6222,6 +6462,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191252</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6339,6 +6584,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191253</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6456,6 +6706,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191254</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6580,6 +6835,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191255</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6701,6 +6961,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191262</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6814,6 +7079,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191258</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6938,8 +7208,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191256</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>